--- a/segments.xlsx
+++ b/segments.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dom.cresswell/Dropbox/Geek/Gaming Projects/Bloodwych 68k/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D6E6F3-036F-7E48-8408-3F25B2EF67E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0B60837-D3F7-8848-8974-5583D3458826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11380" yWindow="880" windowWidth="28780" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17420" yWindow="1100" windowWidth="19040" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BLOODWYCH439" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
-    <sheet name="AI_NAMES" sheetId="2" r:id="rId3"/>
+    <sheet name="AI_NAMES" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BLOODWYCH439!$A$1:$O$2647</definedName>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7634" uniqueCount="3700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7635" uniqueCount="3703">
   <si>
     <t>Type</t>
   </si>
@@ -9724,9 +9723,6 @@
     <t>$A1AA</t>
   </si>
   <si>
-    <t>$460BB</t>
-  </si>
-  <si>
     <t>$31D9C</t>
   </si>
   <si>
@@ -9991,30 +9987,6 @@
     <t>$32BDC</t>
   </si>
   <si>
-    <t>$32E94</t>
-  </si>
-  <si>
-    <t>$3362C</t>
-  </si>
-  <si>
-    <t>$33CE4</t>
-  </si>
-  <si>
-    <t>$37B54</t>
-  </si>
-  <si>
-    <t>$40194</t>
-  </si>
-  <si>
-    <t>$41F94</t>
-  </si>
-  <si>
-    <t>$42F94</t>
-  </si>
-  <si>
-    <t>$42FE4</t>
-  </si>
-  <si>
     <t>$4488C</t>
   </si>
   <si>
@@ -11138,6 +11110,42 @@
   </si>
   <si>
     <t>$4AF0C</t>
+  </si>
+  <si>
+    <t>_DropTheObject</t>
+  </si>
+  <si>
+    <t>_MoveParty</t>
+  </si>
+  <si>
+    <t>_MoveFailed</t>
+  </si>
+  <si>
+    <t>$343F4</t>
+  </si>
+  <si>
+    <t>$346AC</t>
+  </si>
+  <si>
+    <t>$34E44</t>
+  </si>
+  <si>
+    <t>$354FC</t>
+  </si>
+  <si>
+    <t>$3936C</t>
+  </si>
+  <si>
+    <t>$419AC</t>
+  </si>
+  <si>
+    <t>$437AC</t>
+  </si>
+  <si>
+    <t>$447AC</t>
+  </si>
+  <si>
+    <t>$447FC</t>
   </si>
 </sst>
 </file>
@@ -11254,7 +11262,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -11318,12 +11326,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Excel Built-in Normal" xfId="1" xr:uid="{ACE51F02-8306-284E-B6CB-6CB2D79D3F1F}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="40">
+  <dxfs count="6">
     <dxf>
       <font>
         <color theme="3" tint="0.24994659260841701"/>
@@ -11341,325 +11353,6 @@
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="3" tint="0.24994659260841701"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.749961851863155"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="5" tint="-0.24994659260841701"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="3" tint="0.24994659260841701"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.749961851863155"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="5" tint="-0.24994659260841701"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="3" tint="0.24994659260841701"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.749961851863155"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -12037,7 +11730,7 @@
     <col min="2" max="2" width="54.5" customWidth="1"/>
     <col min="3" max="3" width="29.6640625" style="5" customWidth="1"/>
     <col min="4" max="4" width="52.33203125" customWidth="1"/>
-    <col min="5" max="5" width="37.83203125" customWidth="1"/>
+    <col min="5" max="5" width="61.5" customWidth="1"/>
     <col min="6" max="6" width="19.5" customWidth="1"/>
     <col min="7" max="8" width="10.83203125" style="5" customWidth="1"/>
     <col min="9" max="10" width="14.83203125" style="6" customWidth="1"/>
@@ -12075,7 +11768,7 @@
         <v>6</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>3677</v>
+        <v>3668</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
@@ -12727,13 +12420,13 @@
         <v>2263</v>
       </c>
       <c r="B19" t="s">
-        <v>3266</v>
+        <v>3265</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>51</v>
       </c>
       <c r="D19" t="s">
-        <v>3276</v>
+        <v>3275</v>
       </c>
       <c r="E19" t="str">
         <f t="shared" si="0"/>
@@ -12754,7 +12447,7 @@
         <v>4</v>
       </c>
       <c r="L19" t="s">
-        <v>3266</v>
+        <v>3265</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
@@ -12762,13 +12455,13 @@
         <v>2264</v>
       </c>
       <c r="B20" t="s">
-        <v>3265</v>
+        <v>3264</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>51</v>
       </c>
       <c r="D20" t="s">
-        <v>3275</v>
+        <v>3274</v>
       </c>
       <c r="E20" t="str">
         <f t="shared" si="0"/>
@@ -12789,7 +12482,7 @@
         <v>34</v>
       </c>
       <c r="L20" t="s">
-        <v>3265</v>
+        <v>3264</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
@@ -12797,7 +12490,7 @@
         <v>2275</v>
       </c>
       <c r="B21" t="s">
-        <v>3267</v>
+        <v>3266</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>51</v>
@@ -12824,7 +12517,7 @@
         <v>8</v>
       </c>
       <c r="L21" t="s">
-        <v>3267</v>
+        <v>3266</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
@@ -12832,7 +12525,7 @@
         <v>2328</v>
       </c>
       <c r="B22" t="s">
-        <v>3268</v>
+        <v>3267</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>51</v>
@@ -12859,7 +12552,7 @@
         <v>8</v>
       </c>
       <c r="L22" t="s">
-        <v>3268</v>
+        <v>3267</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
@@ -12867,7 +12560,7 @@
         <v>3110</v>
       </c>
       <c r="B23" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>51</v>
@@ -12894,7 +12587,7 @@
         <v>8</v>
       </c>
       <c r="L23" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
@@ -12902,7 +12595,7 @@
         <v>2364</v>
       </c>
       <c r="B24" t="s">
-        <v>3270</v>
+        <v>3269</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>51</v>
@@ -12929,7 +12622,7 @@
         <v>8</v>
       </c>
       <c r="L24" t="s">
-        <v>3270</v>
+        <v>3269</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
@@ -12937,7 +12630,7 @@
         <v>2385</v>
       </c>
       <c r="B25" t="s">
-        <v>3271</v>
+        <v>3270</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>51</v>
@@ -12964,7 +12657,7 @@
         <v>8</v>
       </c>
       <c r="L25" t="s">
-        <v>3271</v>
+        <v>3270</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
@@ -13020,7 +12713,7 @@
         <v>data/characters.heads</v>
       </c>
       <c r="F27" t="s">
-        <v>3230</v>
+        <v>3229</v>
       </c>
       <c r="G27" s="5">
         <f t="shared" si="1"/>
@@ -13042,7 +12735,7 @@
         <v>2902</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>3306</v>
+        <v>3305</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>48</v>
@@ -13069,7 +12762,7 @@
         <v>1B6</v>
       </c>
       <c r="L28" t="s">
-        <v>3306</v>
+        <v>3305</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
@@ -13077,7 +12770,7 @@
         <v>2903</v>
       </c>
       <c r="B29" t="s">
-        <v>3305</v>
+        <v>3304</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>48</v>
@@ -13104,7 +12797,7 @@
         <v>6E</v>
       </c>
       <c r="L29" t="s">
-        <v>3305</v>
+        <v>3304</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
@@ -13112,7 +12805,7 @@
         <v>2897</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>3263</v>
+        <v>3262</v>
       </c>
       <c r="C30" s="13" t="s">
         <v>48</v>
@@ -13121,7 +12814,7 @@
         <v>65</v>
       </c>
       <c r="E30" s="12" t="str">
-        <f t="shared" si="0"/>
+        <f>C30&amp;"/"&amp;D30</f>
         <v>data/objecttext.block</v>
       </c>
       <c r="F30" s="12" t="s">
@@ -13139,7 +12832,7 @@
         <v>262</v>
       </c>
       <c r="L30" t="s">
-        <v>3263</v>
+        <v>3262</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -13147,34 +12840,34 @@
         <v>2905</v>
       </c>
       <c r="B31" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>48</v>
       </c>
       <c r="D31" t="s">
-        <v>3264</v>
-      </c>
-      <c r="E31" t="str">
+        <v>3263</v>
+      </c>
+      <c r="E31" s="27" t="str">
         <f t="shared" si="0"/>
         <v>data/objectfloor.colours</v>
       </c>
       <c r="F31" t="s">
-        <v>3310</v>
+        <v>3309</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" si="1"/>
         <v>58348</v>
       </c>
       <c r="H31" s="5">
-        <v>610</v>
+        <v>110</v>
       </c>
       <c r="I31" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>262</v>
+        <v>6E</v>
       </c>
       <c r="L31" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
@@ -13182,34 +12875,34 @@
         <v>2906</v>
       </c>
       <c r="B32" t="s">
-        <v>3273</v>
+        <v>3272</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>48</v>
       </c>
       <c r="D32" t="s">
-        <v>3274</v>
-      </c>
-      <c r="E32" t="str">
+        <v>3273</v>
+      </c>
+      <c r="E32" s="27" t="str">
         <f t="shared" si="0"/>
         <v>data/objectfloor.palette</v>
       </c>
       <c r="F32" t="s">
-        <v>3309</v>
+        <v>3308</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="1"/>
         <v>58458</v>
       </c>
       <c r="H32" s="5">
-        <v>272</v>
+        <v>172</v>
       </c>
       <c r="I32" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>110</v>
+        <v>AC</v>
       </c>
       <c r="L32" t="s">
-        <v>3273</v>
+        <v>3272</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
@@ -13225,16 +12918,16 @@
       <c r="D33" t="s">
         <v>170</v>
       </c>
-      <c r="E33" t="str">
+      <c r="E33" s="27" t="str">
         <f>C33&amp;"/"&amp;D33</f>
         <v>gfx/ObjectsOnFloor.gfx</v>
       </c>
-      <c r="F33" t="s">
-        <v>3228</v>
+      <c r="F33" s="9" t="s">
+        <v>3315</v>
       </c>
       <c r="G33" s="5">
         <f>IF(F33&lt;&gt;"",HEX2DEC(SUBSTITUTE(SUBSTITUTE(F33,"adrEA",""),"$","")),"")</f>
-        <v>286907</v>
+        <v>207836</v>
       </c>
       <c r="H33" s="5">
         <v>6168</v>
@@ -13260,12 +12953,12 @@
       <c r="D34" t="s">
         <v>171</v>
       </c>
-      <c r="E34" t="str">
+      <c r="E34" s="27" t="str">
         <f>C34&amp;"/"&amp;D34</f>
         <v>gfx/ObjectsOnFloor.offsets</v>
       </c>
       <c r="F34" t="s">
-        <v>3308</v>
+        <v>3307</v>
       </c>
       <c r="G34" s="5">
         <f>IF(F34&lt;&gt;"",HEX2DEC(SUBSTITUTE(SUBSTITUTE(F34,"adrEA",""),"$","")),"")</f>
@@ -13295,23 +12988,23 @@
       <c r="D35" t="s">
         <v>172</v>
       </c>
-      <c r="E35" t="str">
+      <c r="E35" s="27" t="str">
         <f>C35&amp;"/"&amp;D35</f>
         <v>gfx/ObjectsOnFloor.heights</v>
       </c>
       <c r="F35" t="s">
-        <v>3307</v>
+        <v>3306</v>
       </c>
       <c r="G35" s="5">
         <f>IF(F35&lt;&gt;"",HEX2DEC(SUBSTITUTE(SUBSTITUTE(F35,"adrEA",""),"$","")),"")</f>
         <v>58212</v>
       </c>
       <c r="H35" s="5">
-        <v>610</v>
+        <v>136</v>
       </c>
       <c r="I35" s="6" t="str">
         <f>IFERROR(DEC2HEX(H35),"")</f>
-        <v>262</v>
+        <v>88</v>
       </c>
       <c r="L35" t="s">
         <v>3211</v>
@@ -13327,7 +13020,7 @@
         <v>2921</v>
       </c>
       <c r="B37" t="s">
-        <v>3346</v>
+        <v>3337</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>48</v>
@@ -13354,7 +13047,7 @@
         <v>200</v>
       </c>
       <c r="L37" t="s">
-        <v>3346</v>
+        <v>3337</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
@@ -13362,7 +13055,7 @@
         <v>2925</v>
       </c>
       <c r="B38" t="s">
-        <v>3347</v>
+        <v>3338</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>48</v>
@@ -13389,7 +13082,7 @@
         <v>100</v>
       </c>
       <c r="L38" t="s">
-        <v>3347</v>
+        <v>3338</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
@@ -13639,7 +13332,7 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>3353</v>
+        <v>3344</v>
       </c>
       <c r="B46" t="s">
         <v>3109</v>
@@ -13949,7 +13642,7 @@
         <v>C</v>
       </c>
       <c r="J54" s="14" t="s">
-        <v>3690</v>
+        <v>3681</v>
       </c>
       <c r="L54" s="12" t="s">
         <v>3011</v>
@@ -13960,7 +13653,7 @@
         <v>3011</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>3691</v>
+        <v>3682</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>8</v>
@@ -13987,7 +13680,7 @@
         <v>2</v>
       </c>
       <c r="J55" s="26" t="s">
-        <v>3676</v>
+        <v>3667</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="17" x14ac:dyDescent="0.25">
@@ -13995,7 +13688,7 @@
         <v>3011</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>3692</v>
+        <v>3683</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>8</v>
@@ -14022,7 +13715,7 @@
         <v>2</v>
       </c>
       <c r="J56" s="26" t="s">
-        <v>3683</v>
+        <v>3674</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="17" x14ac:dyDescent="0.25">
@@ -14030,7 +13723,7 @@
         <v>3011</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>3693</v>
+        <v>3684</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>8</v>
@@ -14057,7 +13750,7 @@
         <v>2</v>
       </c>
       <c r="J57" s="26" t="s">
-        <v>3683</v>
+        <v>3674</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="17" x14ac:dyDescent="0.25">
@@ -14065,7 +13758,7 @@
         <v>3011</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>3694</v>
+        <v>3685</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>8</v>
@@ -14092,7 +13785,7 @@
         <v>2</v>
       </c>
       <c r="J58" s="26" t="s">
-        <v>3683</v>
+        <v>3674</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="17" x14ac:dyDescent="0.25">
@@ -14100,7 +13793,7 @@
         <v>3011</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>3695</v>
+        <v>3686</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>8</v>
@@ -14127,7 +13820,7 @@
         <v>2</v>
       </c>
       <c r="J59" s="26" t="s">
-        <v>3683</v>
+        <v>3674</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="17" x14ac:dyDescent="0.25">
@@ -14135,7 +13828,7 @@
         <v>3011</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>3696</v>
+        <v>3687</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>8</v>
@@ -14162,7 +13855,7 @@
         <v>2</v>
       </c>
       <c r="J60" s="26" t="s">
-        <v>3683</v>
+        <v>3674</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.2">
@@ -14197,7 +13890,7 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="12" t="s">
-        <v>3352</v>
+        <v>3343</v>
       </c>
       <c r="B62" s="9"/>
       <c r="C62" s="5" t="s">
@@ -14227,7 +13920,7 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" s="12" t="s">
-        <v>3352</v>
+        <v>3343</v>
       </c>
       <c r="B63" s="9"/>
       <c r="C63" s="5" t="s">
@@ -14257,7 +13950,7 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" s="12" t="s">
-        <v>3352</v>
+        <v>3343</v>
       </c>
       <c r="B64" s="9"/>
       <c r="C64" s="5" t="s">
@@ -14287,7 +13980,7 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A65" s="12" t="s">
-        <v>3352</v>
+        <v>3343</v>
       </c>
       <c r="B65" s="9"/>
       <c r="C65" s="5" t="s">
@@ -14317,7 +14010,7 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A66" s="12" t="s">
-        <v>3352</v>
+        <v>3343</v>
       </c>
       <c r="B66" s="9"/>
       <c r="C66" s="5" t="s">
@@ -14410,7 +14103,7 @@
         <v>gfx/ButtonHighlights.gfx</v>
       </c>
       <c r="F68" t="s">
-        <v>3232</v>
+        <v>3231</v>
       </c>
       <c r="G68" s="5">
         <f>IF(F68&lt;&gt;"",HEX2DEC(SUBSTITUTE(SUBSTITUTE(F68,"adrEA",""),"$","")),"")</f>
@@ -14443,7 +14136,7 @@
         <v>18B7A</v>
       </c>
       <c r="Q68" t="s">
-        <v>3231</v>
+        <v>3230</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.2">
@@ -14464,7 +14157,7 @@
         <v>gfx/Scroll_Edge_Top.gfx</v>
       </c>
       <c r="F69" t="s">
-        <v>3233</v>
+        <v>3232</v>
       </c>
       <c r="G69" s="5">
         <f>IF(F69&lt;&gt;"",HEX2DEC(SUBSTITUTE(SUBSTITUTE(F69,"adrEA",""),"$","")),"")</f>
@@ -14515,7 +14208,7 @@
         <v>gfx/Scroll_Edge_Bottom.gfx</v>
       </c>
       <c r="F70" t="s">
-        <v>3234</v>
+        <v>3233</v>
       </c>
       <c r="G70" s="5">
         <f>IF(F70&lt;&gt;"",HEX2DEC(SUBSTITUTE(SUBSTITUTE(F70,"adrEA",""),"$","")),"")</f>
@@ -14566,7 +14259,7 @@
         <v>gfx/Scroll_Edge_Left.gfx</v>
       </c>
       <c r="F71" t="s">
-        <v>3235</v>
+        <v>3234</v>
       </c>
       <c r="G71" s="5">
         <f>IF(F71&lt;&gt;"",HEX2DEC(SUBSTITUTE(SUBSTITUTE(F71,"adrEA",""),"$","")),"")</f>
@@ -14617,7 +14310,7 @@
         <v>gfx/Scroll_Edge_Right.gfx</v>
       </c>
       <c r="F72" t="s">
-        <v>3236</v>
+        <v>3235</v>
       </c>
       <c r="G72" s="5">
         <f>G71+H71</f>
@@ -14668,7 +14361,7 @@
         <v>gfx/Shield_Clicked.gfx</v>
       </c>
       <c r="F73" t="s">
-        <v>3237</v>
+        <v>3236</v>
       </c>
       <c r="G73" s="5">
         <f>G72+H72</f>
@@ -15077,7 +14770,7 @@
         <v>gfx/Stairs_Up.gfx</v>
       </c>
       <c r="F84" t="s">
-        <v>3240</v>
+        <v>3239</v>
       </c>
       <c r="G84" s="5">
         <f t="shared" si="12"/>
@@ -15094,7 +14787,7 @@
         <v>3186</v>
       </c>
       <c r="N84" s="20" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="O84">
         <f>HEX2DEC(N84)</f>
@@ -15140,7 +14833,7 @@
         <v>2A7B4</v>
       </c>
       <c r="N85" t="s">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="O85">
         <f>HEX2DEC(N85)</f>
@@ -15274,7 +14967,7 @@
         <v>gfx/Pad_Pit_Low.gfx</v>
       </c>
       <c r="F89" t="s">
-        <v>3313</v>
+        <v>3312</v>
       </c>
       <c r="G89" s="5">
         <f t="shared" si="12"/>
@@ -15309,7 +15002,7 @@
         <v>gfx/Pad_Pit_High.gfx</v>
       </c>
       <c r="F90" t="s">
-        <v>3314</v>
+        <v>3313</v>
       </c>
       <c r="G90" s="5">
         <f t="shared" si="12"/>
@@ -15344,7 +15037,7 @@
         <v>gfx/Pad_Trigger.gfx</v>
       </c>
       <c r="F91" t="s">
-        <v>3315</v>
+        <v>3314</v>
       </c>
       <c r="G91" s="5">
         <f t="shared" si="12"/>
@@ -15379,7 +15072,7 @@
         <v>gfx/FloorCeiling.gfx</v>
       </c>
       <c r="F92" t="s">
-        <v>3229</v>
+        <v>3228</v>
       </c>
       <c r="G92" s="5">
         <f t="shared" si="12"/>
@@ -15413,12 +15106,12 @@
         <f t="shared" si="11"/>
         <v>gfx/AirbourneFireball.gfx</v>
       </c>
-      <c r="F93" t="s">
-        <v>3316</v>
+      <c r="F93" s="9" t="s">
+        <v>3694</v>
       </c>
       <c r="G93" s="5">
         <f t="shared" si="12"/>
-        <v>207836</v>
+        <v>214004</v>
       </c>
       <c r="H93" s="5" t="s">
         <v>174</v>
@@ -15448,12 +15141,12 @@
         <f t="shared" si="11"/>
         <v>gfx/AirbourneSpells.gfx</v>
       </c>
-      <c r="F94" t="s">
-        <v>3317</v>
+      <c r="F94" s="9" t="s">
+        <v>3695</v>
       </c>
       <c r="G94" s="5">
         <f t="shared" si="12"/>
-        <v>208532</v>
+        <v>214700</v>
       </c>
       <c r="H94" s="5">
         <v>1944</v>
@@ -15483,12 +15176,12 @@
         <f t="shared" si="11"/>
         <v>data/characters.colours</v>
       </c>
-      <c r="F95" t="s">
-        <v>3318</v>
+      <c r="F95" s="9" t="s">
+        <v>3696</v>
       </c>
       <c r="G95" s="5">
         <f t="shared" si="12"/>
-        <v>210476</v>
+        <v>216644</v>
       </c>
       <c r="H95" s="5">
         <v>1720</v>
@@ -15519,11 +15212,11 @@
         <v>gfx/HeadParts.gfx</v>
       </c>
       <c r="F96" t="s">
-        <v>3319</v>
+        <v>3697</v>
       </c>
       <c r="G96" s="5">
         <f t="shared" si="12"/>
-        <v>212196</v>
+        <v>218364</v>
       </c>
       <c r="H96" s="5">
         <v>15984</v>
@@ -15554,11 +15247,11 @@
         <v>gfx/BodyParts.gfx</v>
       </c>
       <c r="F97" t="s">
-        <v>3320</v>
+        <v>3698</v>
       </c>
       <c r="G97" s="5">
         <f t="shared" si="12"/>
-        <v>228180</v>
+        <v>234348</v>
       </c>
       <c r="H97" s="5">
         <v>34368</v>
@@ -15589,11 +15282,11 @@
         <v>gfx/Avatars_Large.gfx</v>
       </c>
       <c r="F98" t="s">
-        <v>3321</v>
+        <v>3699</v>
       </c>
       <c r="G98" s="5">
         <f t="shared" si="12"/>
-        <v>262548</v>
+        <v>268716</v>
       </c>
       <c r="H98" s="5">
         <v>7680</v>
@@ -15624,11 +15317,11 @@
         <v>gfx/Shield_Avatars.gfx</v>
       </c>
       <c r="F99" t="s">
-        <v>3322</v>
+        <v>3700</v>
       </c>
       <c r="G99" s="5">
         <f t="shared" si="12"/>
-        <v>270228</v>
+        <v>276396</v>
       </c>
       <c r="H99" s="5">
         <v>4096</v>
@@ -15659,11 +15352,11 @@
         <v>gfx/ShieldTop.gfx</v>
       </c>
       <c r="F100" t="s">
-        <v>3323</v>
+        <v>3701</v>
       </c>
       <c r="G100" s="5">
         <f t="shared" si="12"/>
-        <v>274324</v>
+        <v>280492</v>
       </c>
       <c r="H100" s="5" t="s">
         <v>181</v>
@@ -15694,11 +15387,11 @@
         <v>gfx/ShieldBottom.gfx</v>
       </c>
       <c r="F101" t="s">
-        <v>3324</v>
+        <v>3702</v>
       </c>
       <c r="G101" s="5">
         <f t="shared" si="12"/>
-        <v>274404</v>
+        <v>280572</v>
       </c>
       <c r="H101" s="5" t="s">
         <v>183</v>
@@ -15729,7 +15422,7 @@
         <v>gfx/ShieldClasses.gfx</v>
       </c>
       <c r="F102" t="s">
-        <v>3325</v>
+        <v>3316</v>
       </c>
       <c r="G102" s="5">
         <f t="shared" si="12"/>
@@ -15764,7 +15457,7 @@
         <v>gfx/Fairy.gfx</v>
       </c>
       <c r="F103" t="s">
-        <v>3326</v>
+        <v>3317</v>
       </c>
       <c r="G103" s="5">
         <f t="shared" si="12"/>
@@ -15783,7 +15476,7 @@
     </row>
     <row r="104" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A104" s="9" t="s">
-        <v>3352</v>
+        <v>3343</v>
       </c>
       <c r="C104" s="23" t="s">
         <v>51</v>
@@ -15808,7 +15501,7 @@
       </c>
       <c r="J104" s="24"/>
       <c r="O104" s="9" t="s">
-        <v>3241</v>
+        <v>3240</v>
       </c>
     </row>
     <row r="105" spans="1:22" x14ac:dyDescent="0.2">
@@ -15828,26 +15521,26 @@
         <v>328450</v>
       </c>
       <c r="K105">
-        <f>M105-$M$187</f>
+        <f t="shared" ref="K105:K117" si="16">M105-$M$187</f>
         <v>16260</v>
       </c>
       <c r="L105" t="s">
-        <v>3553</v>
+        <v>3544</v>
       </c>
       <c r="M105">
-        <f t="shared" ref="M105:M117" si="16">(HEX2DEC(SUBSTITUTE(F105,"$","")))</f>
+        <f t="shared" ref="M105:M117" si="17">(HEX2DEC(SUBSTITUTE(F105,"$","")))</f>
         <v>328450</v>
       </c>
       <c r="O105" t="str">
-        <f>DEC2HEX((HEX2DEC($O$187)+HEX2DEC(RIGHT(A105,5))-HEX2DEC($O$187)))</f>
+        <f t="shared" ref="O105:O117" si="18">DEC2HEX((HEX2DEC($O$187)+HEX2DEC(RIGHT(A105,5))-HEX2DEC($O$187)))</f>
         <v>50302</v>
       </c>
       <c r="P105">
-        <f>HEX2DEC(O105)-HEX2DEC($O$187)</f>
+        <f t="shared" ref="P105:P117" si="19">HEX2DEC(O105)-HEX2DEC($O$187)</f>
         <v>15360</v>
       </c>
       <c r="T105" s="17" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="V105" t="str">
         <f>RIGHT(T105,4)</f>
@@ -15859,7 +15552,7 @@
         <v>3078</v>
       </c>
       <c r="B106" s="25" t="str">
-        <f t="shared" ref="B106:B117" si="17">"_Offset_GFX_Pockets_0x"&amp;V106</f>
+        <f t="shared" ref="B106:B117" si="20">"_Offset_GFX_Pockets_0x"&amp;V106</f>
         <v>_Offset_GFX_Pockets_0x3C30</v>
       </c>
       <c r="F106" t="str">
@@ -15871,29 +15564,29 @@
         <v>328498</v>
       </c>
       <c r="K106">
-        <f>M106-$M$187</f>
+        <f t="shared" si="16"/>
         <v>16308</v>
       </c>
       <c r="L106" t="s">
-        <v>3554</v>
+        <v>3545</v>
       </c>
       <c r="M106">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>328498</v>
       </c>
       <c r="O106" t="str">
-        <f>DEC2HEX((HEX2DEC($O$187)+HEX2DEC(RIGHT(A106,5))-HEX2DEC($O$187)))</f>
+        <f t="shared" si="18"/>
         <v>50332</v>
       </c>
       <c r="P106">
-        <f>HEX2DEC(O106)-HEX2DEC($O$187)</f>
+        <f t="shared" si="19"/>
         <v>15408</v>
       </c>
       <c r="T106" s="17" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="V106" t="str">
-        <f t="shared" ref="V106:V117" si="18">RIGHT(T106,4)</f>
+        <f t="shared" ref="V106:V117" si="21">RIGHT(T106,4)</f>
         <v>3C30</v>
       </c>
     </row>
@@ -15902,7 +15595,7 @@
         <v>3079</v>
       </c>
       <c r="B107" s="25" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>_Offset_GFX_Pockets_0x3C60</v>
       </c>
       <c r="F107" t="str">
@@ -15914,29 +15607,29 @@
         <v>328546</v>
       </c>
       <c r="K107">
-        <f>M107-$M$187</f>
+        <f t="shared" si="16"/>
         <v>16356</v>
       </c>
       <c r="L107" t="s">
-        <v>3555</v>
+        <v>3546</v>
       </c>
       <c r="M107">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>328546</v>
       </c>
       <c r="O107" t="str">
-        <f>DEC2HEX((HEX2DEC($O$187)+HEX2DEC(RIGHT(A107,5))-HEX2DEC($O$187)))</f>
+        <f t="shared" si="18"/>
         <v>50362</v>
       </c>
       <c r="P107">
-        <f>HEX2DEC(O107)-HEX2DEC($O$187)</f>
+        <f t="shared" si="19"/>
         <v>15456</v>
       </c>
       <c r="T107" s="17" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="V107" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>3C60</v>
       </c>
     </row>
@@ -15945,7 +15638,7 @@
         <v>3080</v>
       </c>
       <c r="B108" s="25" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>_Offset_GFX_Pockets_0x4100</v>
       </c>
       <c r="F108" t="str">
@@ -15957,29 +15650,29 @@
         <v>329730</v>
       </c>
       <c r="K108">
-        <f>M108-$M$187</f>
+        <f t="shared" si="16"/>
         <v>17540</v>
       </c>
       <c r="L108" t="s">
-        <v>3556</v>
+        <v>3547</v>
       </c>
       <c r="M108">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>329730</v>
       </c>
       <c r="O108" t="str">
-        <f>DEC2HEX((HEX2DEC($O$187)+HEX2DEC(RIGHT(A108,5))-HEX2DEC($O$187)))</f>
+        <f t="shared" si="18"/>
         <v>50802</v>
       </c>
       <c r="P108">
-        <f>HEX2DEC(O108)-HEX2DEC($O$187)</f>
+        <f t="shared" si="19"/>
         <v>16640</v>
       </c>
       <c r="T108" s="17" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
       <c r="V108" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>4100</v>
       </c>
     </row>
@@ -15988,7 +15681,7 @@
         <v>3081</v>
       </c>
       <c r="B109" s="25" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>_Offset_GFX_Pockets_0x4130</v>
       </c>
       <c r="F109" t="str">
@@ -16000,29 +15693,29 @@
         <v>329778</v>
       </c>
       <c r="K109">
-        <f>M109-$M$187</f>
+        <f t="shared" si="16"/>
         <v>17588</v>
       </c>
       <c r="L109" t="s">
-        <v>3557</v>
+        <v>3548</v>
       </c>
       <c r="M109">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>329778</v>
       </c>
       <c r="O109" t="str">
-        <f>DEC2HEX((HEX2DEC($O$187)+HEX2DEC(RIGHT(A109,5))-HEX2DEC($O$187)))</f>
+        <f t="shared" si="18"/>
         <v>50832</v>
       </c>
       <c r="P109">
-        <f>HEX2DEC(O109)-HEX2DEC($O$187)</f>
+        <f t="shared" si="19"/>
         <v>16688</v>
       </c>
       <c r="T109" s="17" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="V109" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>4130</v>
       </c>
     </row>
@@ -16031,7 +15724,7 @@
         <v>3082</v>
       </c>
       <c r="B110" s="25" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>_Offset_GFX_Pockets_0x5070</v>
       </c>
       <c r="F110" t="str">
@@ -16043,29 +15736,29 @@
         <v>333682</v>
       </c>
       <c r="K110">
-        <f>M110-$M$187</f>
+        <f t="shared" si="16"/>
         <v>21492</v>
       </c>
       <c r="L110" t="s">
-        <v>3558</v>
+        <v>3549</v>
       </c>
       <c r="M110">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>333682</v>
       </c>
       <c r="O110" t="str">
-        <f>DEC2HEX((HEX2DEC($O$187)+HEX2DEC(RIGHT(A110,5))-HEX2DEC($O$187)))</f>
+        <f t="shared" si="18"/>
         <v>51772</v>
       </c>
       <c r="P110">
-        <f>HEX2DEC(O110)-HEX2DEC($O$187)</f>
+        <f t="shared" si="19"/>
         <v>20592</v>
       </c>
       <c r="T110" s="17" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
       <c r="V110" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>5070</v>
       </c>
     </row>
@@ -16074,7 +15767,7 @@
         <v>3083</v>
       </c>
       <c r="B111" s="25" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>_Offset_GFX_Pockets_0x6500</v>
       </c>
       <c r="F111" t="str">
@@ -16086,29 +15779,29 @@
         <v>338946</v>
       </c>
       <c r="K111">
-        <f>M111-$M$187</f>
+        <f t="shared" si="16"/>
         <v>26756</v>
       </c>
       <c r="L111" t="s">
-        <v>3559</v>
+        <v>3550</v>
       </c>
       <c r="M111">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>338946</v>
       </c>
       <c r="O111" t="str">
-        <f>DEC2HEX((HEX2DEC($O$187)+HEX2DEC(RIGHT(A111,5))-HEX2DEC($O$187)))</f>
+        <f t="shared" si="18"/>
         <v>52C02</v>
       </c>
       <c r="P111">
-        <f>HEX2DEC(O111)-HEX2DEC($O$187)</f>
+        <f t="shared" si="19"/>
         <v>25856</v>
       </c>
       <c r="T111" s="17" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="V111" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>6500</v>
       </c>
     </row>
@@ -16117,7 +15810,7 @@
         <v>3084</v>
       </c>
       <c r="B112" s="25" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>_Offset_GFX_Pockets_0x6508</v>
       </c>
       <c r="F112" t="str">
@@ -16129,29 +15822,29 @@
         <v>338954</v>
       </c>
       <c r="K112">
-        <f>M112-$M$187</f>
+        <f t="shared" si="16"/>
         <v>26764</v>
       </c>
       <c r="L112" t="s">
-        <v>3560</v>
+        <v>3551</v>
       </c>
       <c r="M112">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>338954</v>
       </c>
       <c r="O112" t="str">
-        <f>DEC2HEX((HEX2DEC($O$187)+HEX2DEC(RIGHT(A112,5))-HEX2DEC($O$187)))</f>
+        <f t="shared" si="18"/>
         <v>52C0A</v>
       </c>
       <c r="P112">
-        <f>HEX2DEC(O112)-HEX2DEC($O$187)</f>
+        <f t="shared" si="19"/>
         <v>25864</v>
       </c>
       <c r="T112" s="17" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
       <c r="V112" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>6508</v>
       </c>
     </row>
@@ -16160,7 +15853,7 @@
         <v>3085</v>
       </c>
       <c r="B113" s="25" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>_Offset_GFX_Pockets_0x67C0</v>
       </c>
       <c r="F113" t="str">
@@ -16172,29 +15865,29 @@
         <v>339650</v>
       </c>
       <c r="K113">
-        <f>M113-$M$187</f>
+        <f t="shared" si="16"/>
         <v>27460</v>
       </c>
       <c r="L113" t="s">
-        <v>3561</v>
+        <v>3552</v>
       </c>
       <c r="M113">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>339650</v>
       </c>
       <c r="O113" t="str">
-        <f>DEC2HEX((HEX2DEC($O$187)+HEX2DEC(RIGHT(A113,5))-HEX2DEC($O$187)))</f>
+        <f t="shared" si="18"/>
         <v>52EC2</v>
       </c>
       <c r="P113">
-        <f>HEX2DEC(O113)-HEX2DEC($O$187)</f>
+        <f t="shared" si="19"/>
         <v>26560</v>
       </c>
       <c r="T113" s="17" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="V113" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>67C0</v>
       </c>
     </row>
@@ -16203,7 +15896,7 @@
         <v>3086</v>
       </c>
       <c r="B114" s="25" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>_Offset_GFX_Pockets_0x67E0</v>
       </c>
       <c r="F114" t="str">
@@ -16215,29 +15908,29 @@
         <v>339682</v>
       </c>
       <c r="K114">
-        <f>M114-$M$187</f>
+        <f t="shared" si="16"/>
         <v>27492</v>
       </c>
       <c r="L114" t="s">
-        <v>3562</v>
+        <v>3553</v>
       </c>
       <c r="M114">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>339682</v>
       </c>
       <c r="O114" t="str">
-        <f>DEC2HEX((HEX2DEC($O$187)+HEX2DEC(RIGHT(A114,5))-HEX2DEC($O$187)))</f>
+        <f t="shared" si="18"/>
         <v>52EE2</v>
       </c>
       <c r="P114">
-        <f>HEX2DEC(O114)-HEX2DEC($O$187)</f>
+        <f t="shared" si="19"/>
         <v>26592</v>
       </c>
       <c r="T114" s="17" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="V114" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>67E0</v>
       </c>
     </row>
@@ -16246,7 +15939,7 @@
         <v>3087</v>
       </c>
       <c r="B115" s="25" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>_Offset_GFX_Pockets_0x6A60</v>
       </c>
       <c r="F115" t="str">
@@ -16258,29 +15951,29 @@
         <v>340322</v>
       </c>
       <c r="K115">
-        <f>M115-$M$187</f>
+        <f t="shared" si="16"/>
         <v>28132</v>
       </c>
       <c r="L115" t="s">
-        <v>3563</v>
+        <v>3554</v>
       </c>
       <c r="M115">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>340322</v>
       </c>
       <c r="O115" t="str">
-        <f>DEC2HEX((HEX2DEC($O$187)+HEX2DEC(RIGHT(A115,5))-HEX2DEC($O$187)))</f>
+        <f t="shared" si="18"/>
         <v>53162</v>
       </c>
       <c r="P115">
-        <f>HEX2DEC(O115)-HEX2DEC($O$187)</f>
+        <f t="shared" si="19"/>
         <v>27232</v>
       </c>
       <c r="T115" s="17" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="V115" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>6A60</v>
       </c>
     </row>
@@ -16289,7 +15982,7 @@
         <v>3088</v>
       </c>
       <c r="B116" s="25" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>_Offset_GFX_Pockets_0x7580</v>
       </c>
       <c r="F116" t="str">
@@ -16301,29 +15994,29 @@
         <v>343170</v>
       </c>
       <c r="K116">
-        <f>M116-$M$187</f>
+        <f t="shared" si="16"/>
         <v>30980</v>
       </c>
       <c r="L116" t="s">
-        <v>3564</v>
+        <v>3555</v>
       </c>
       <c r="M116">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>343170</v>
       </c>
       <c r="O116" t="str">
-        <f>DEC2HEX((HEX2DEC($O$187)+HEX2DEC(RIGHT(A116,5))-HEX2DEC($O$187)))</f>
+        <f t="shared" si="18"/>
         <v>53C82</v>
       </c>
       <c r="P116">
-        <f>HEX2DEC(O116)-HEX2DEC($O$187)</f>
+        <f t="shared" si="19"/>
         <v>30080</v>
       </c>
       <c r="T116" s="17" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="V116" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>7580</v>
       </c>
     </row>
@@ -16332,7 +16025,7 @@
         <v>3089</v>
       </c>
       <c r="B117" s="25" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>_Offset_GFX_Pockets_0x7688</v>
       </c>
       <c r="F117" t="str">
@@ -16344,29 +16037,29 @@
         <v>343434</v>
       </c>
       <c r="K117">
-        <f>M117-$M$187</f>
+        <f t="shared" si="16"/>
         <v>31244</v>
       </c>
       <c r="L117" t="s">
-        <v>3565</v>
+        <v>3556</v>
       </c>
       <c r="M117">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>343434</v>
       </c>
       <c r="O117" t="str">
-        <f>DEC2HEX((HEX2DEC($O$187)+HEX2DEC(RIGHT(A117,5))-HEX2DEC($O$187)))</f>
+        <f t="shared" si="18"/>
         <v>53D8A</v>
       </c>
       <c r="P117">
-        <f>HEX2DEC(O117)-HEX2DEC($O$187)</f>
+        <f t="shared" si="19"/>
         <v>30344</v>
       </c>
       <c r="T117" s="17" t="s">
-        <v>3256</v>
+        <v>3255</v>
       </c>
       <c r="V117" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>7688</v>
       </c>
     </row>
@@ -16419,21 +16112,21 @@
         <v>213</v>
       </c>
       <c r="E119" t="str">
-        <f t="shared" ref="E119:E135" si="19">C119&amp;"/"&amp;D119</f>
+        <f t="shared" ref="E119:E135" si="22">C119&amp;"/"&amp;D119</f>
         <v>gfx/Misc_Pillar.offsets</v>
       </c>
       <c r="F119" t="s">
         <v>214</v>
       </c>
       <c r="G119" s="5">
-        <f t="shared" ref="G119:G135" si="20">IF(F119&lt;&gt;"",HEX2DEC(SUBSTITUTE(SUBSTITUTE(F119,"adrEA",""),"$","")),"")</f>
+        <f t="shared" ref="G119:G135" si="23">IF(F119&lt;&gt;"",HEX2DEC(SUBSTITUTE(SUBSTITUTE(F119,"adrEA",""),"$","")),"")</f>
         <v>100242</v>
       </c>
       <c r="H119" s="5">
         <v>22</v>
       </c>
       <c r="I119" s="6" t="str">
-        <f t="shared" ref="I119:I135" si="21">IFERROR(DEC2HEX(H119),"")</f>
+        <f t="shared" ref="I119:I135" si="24">IFERROR(DEC2HEX(H119),"")</f>
         <v>16</v>
       </c>
       <c r="L119" t="s">
@@ -16454,21 +16147,21 @@
         <v>216</v>
       </c>
       <c r="E120" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>gfx/Misc_Bed.offsets</v>
       </c>
       <c r="F120" t="s">
         <v>217</v>
       </c>
       <c r="G120" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>100264</v>
       </c>
       <c r="H120" s="5">
         <v>36</v>
       </c>
       <c r="I120" s="6" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>24</v>
       </c>
       <c r="L120" t="s">
@@ -16480,7 +16173,7 @@
         <v>221</v>
       </c>
       <c r="B121" t="s">
-        <v>3303</v>
+        <v>3302</v>
       </c>
       <c r="C121" s="5" t="s">
         <v>124</v>
@@ -16489,25 +16182,25 @@
         <v>219</v>
       </c>
       <c r="E121" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>gfx/Wooden_Doors.offsets</v>
       </c>
       <c r="F121" t="s">
         <v>220</v>
       </c>
       <c r="G121" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>100300</v>
       </c>
       <c r="H121" s="5">
         <v>32</v>
       </c>
       <c r="I121" s="6" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
       <c r="L121" t="s">
-        <v>3303</v>
+        <v>3302</v>
       </c>
     </row>
     <row r="122" spans="1:22" x14ac:dyDescent="0.2">
@@ -16515,7 +16208,7 @@
         <v>224</v>
       </c>
       <c r="B122" t="s">
-        <v>3277</v>
+        <v>3276</v>
       </c>
       <c r="C122" s="5" t="s">
         <v>124</v>
@@ -16524,25 +16217,25 @@
         <v>222</v>
       </c>
       <c r="E122" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>gfx/Wooden_Wall.offsets</v>
       </c>
       <c r="F122" t="s">
         <v>223</v>
       </c>
       <c r="G122" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>100332</v>
       </c>
       <c r="H122" s="5">
         <v>32</v>
       </c>
       <c r="I122" s="6" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
       <c r="L122" t="s">
-        <v>3277</v>
+        <v>3276</v>
       </c>
     </row>
     <row r="123" spans="1:22" x14ac:dyDescent="0.2">
@@ -16550,7 +16243,7 @@
         <v>227</v>
       </c>
       <c r="B123" t="s">
-        <v>3278</v>
+        <v>3277</v>
       </c>
       <c r="C123" s="5" t="s">
         <v>124</v>
@@ -16559,25 +16252,25 @@
         <v>225</v>
       </c>
       <c r="E123" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>gfx/Main_Shelf.offsets</v>
       </c>
       <c r="F123" t="s">
         <v>226</v>
       </c>
       <c r="G123" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>100364</v>
       </c>
       <c r="H123" s="5">
         <v>32</v>
       </c>
       <c r="I123" s="6" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
       <c r="L123" t="s">
-        <v>3278</v>
+        <v>3277</v>
       </c>
     </row>
     <row r="124" spans="1:22" x14ac:dyDescent="0.2">
@@ -16585,7 +16278,7 @@
         <v>230</v>
       </c>
       <c r="B124" t="s">
-        <v>3279</v>
+        <v>3278</v>
       </c>
       <c r="C124" s="5" t="s">
         <v>124</v>
@@ -16594,25 +16287,25 @@
         <v>228</v>
       </c>
       <c r="E124" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>gfx/Main_Sign.offsets</v>
       </c>
       <c r="F124" t="s">
         <v>229</v>
       </c>
       <c r="G124" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>100396</v>
       </c>
       <c r="H124" s="5">
         <v>32</v>
       </c>
       <c r="I124" s="6" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
       <c r="L124" t="s">
-        <v>3279</v>
+        <v>3278</v>
       </c>
     </row>
     <row r="125" spans="1:22" x14ac:dyDescent="0.2">
@@ -16620,7 +16313,7 @@
         <v>233</v>
       </c>
       <c r="B125" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
       <c r="C125" s="5" t="s">
         <v>124</v>
@@ -16629,25 +16322,25 @@
         <v>231</v>
       </c>
       <c r="E125" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>gfx/Stairs_Up.offsets</v>
       </c>
       <c r="F125" t="s">
         <v>232</v>
       </c>
       <c r="G125" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>100428</v>
       </c>
       <c r="H125" s="5">
         <v>34</v>
       </c>
       <c r="I125" s="6" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>22</v>
       </c>
       <c r="L125" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
     </row>
     <row r="126" spans="1:22" x14ac:dyDescent="0.2">
@@ -16655,7 +16348,7 @@
         <v>236</v>
       </c>
       <c r="B126" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
       <c r="C126" s="5" t="s">
         <v>124</v>
@@ -16664,25 +16357,25 @@
         <v>234</v>
       </c>
       <c r="E126" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>gfx/Stairs_Down.offsets</v>
       </c>
       <c r="F126" t="s">
         <v>235</v>
       </c>
       <c r="G126" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>100462</v>
       </c>
       <c r="H126" s="5">
         <v>34</v>
       </c>
       <c r="I126" s="6" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>22</v>
       </c>
       <c r="L126" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
     </row>
     <row r="127" spans="1:22" x14ac:dyDescent="0.2">
@@ -16690,7 +16383,7 @@
         <v>239</v>
       </c>
       <c r="B127" t="s">
-        <v>3282</v>
+        <v>3281</v>
       </c>
       <c r="C127" s="5" t="s">
         <v>124</v>
@@ -16699,25 +16392,25 @@
         <v>237</v>
       </c>
       <c r="E127" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>gfx/Door.offsets</v>
       </c>
       <c r="F127" t="s">
         <v>238</v>
       </c>
       <c r="G127" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>100496</v>
       </c>
       <c r="H127" s="5">
         <v>26</v>
       </c>
       <c r="I127" s="6" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>1A</v>
       </c>
       <c r="L127" t="s">
-        <v>3282</v>
+        <v>3281</v>
       </c>
     </row>
     <row r="128" spans="1:22" x14ac:dyDescent="0.2">
@@ -16725,7 +16418,7 @@
         <v>242</v>
       </c>
       <c r="B128" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="C128" s="5" t="s">
         <v>124</v>
@@ -16734,25 +16427,25 @@
         <v>240</v>
       </c>
       <c r="E128" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>gfx/Main_Switches.offsets</v>
       </c>
       <c r="F128" t="s">
         <v>241</v>
       </c>
       <c r="G128" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>100522</v>
       </c>
       <c r="H128" s="5">
         <v>32</v>
       </c>
       <c r="I128" s="6" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
       <c r="L128" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.2">
@@ -16760,7 +16453,7 @@
         <v>245</v>
       </c>
       <c r="B129" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
       <c r="C129" s="5" t="s">
         <v>124</v>
@@ -16769,25 +16462,25 @@
         <v>243</v>
       </c>
       <c r="E129" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>gfx/Pad_Pit.offsets</v>
       </c>
       <c r="F129" t="s">
         <v>244</v>
       </c>
       <c r="G129" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>100554</v>
       </c>
       <c r="H129" s="5">
         <v>24</v>
       </c>
       <c r="I129" s="6" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>18</v>
       </c>
       <c r="L129" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.2">
@@ -16795,7 +16488,7 @@
         <v>248</v>
       </c>
       <c r="B130" t="s">
-        <v>3285</v>
+        <v>3284</v>
       </c>
       <c r="C130" s="5" t="s">
         <v>124</v>
@@ -16804,25 +16497,25 @@
         <v>246</v>
       </c>
       <c r="E130" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>gfx/Pad_Trigger.offsets</v>
       </c>
       <c r="F130" t="s">
         <v>247</v>
       </c>
       <c r="G130" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>100578</v>
       </c>
       <c r="H130" s="5">
         <v>24</v>
       </c>
       <c r="I130" s="6" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>18</v>
       </c>
       <c r="L130" t="s">
-        <v>3285</v>
+        <v>3284</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.2">
@@ -16830,7 +16523,7 @@
         <v>251</v>
       </c>
       <c r="B131" t="s">
-        <v>3286</v>
+        <v>3285</v>
       </c>
       <c r="C131" s="5" t="s">
         <v>124</v>
@@ -16839,25 +16532,25 @@
         <v>249</v>
       </c>
       <c r="E131" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>gfx/Main_Walls.positions</v>
       </c>
       <c r="F131" t="s">
         <v>250</v>
       </c>
       <c r="G131" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>46778</v>
       </c>
       <c r="H131" s="5">
         <v>112</v>
       </c>
       <c r="I131" s="6" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>70</v>
       </c>
       <c r="L131" t="s">
-        <v>3286</v>
+        <v>3285</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.2">
@@ -16865,7 +16558,7 @@
         <v>254</v>
       </c>
       <c r="B132" t="s">
-        <v>3287</v>
+        <v>3286</v>
       </c>
       <c r="C132" s="5" t="s">
         <v>124</v>
@@ -16874,25 +16567,25 @@
         <v>252</v>
       </c>
       <c r="E132" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>gfx/Wooden_Wall.positions</v>
       </c>
       <c r="F132" t="s">
         <v>253</v>
       </c>
       <c r="G132" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>46890</v>
       </c>
       <c r="H132" s="5">
         <v>112</v>
       </c>
       <c r="I132" s="6" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>70</v>
       </c>
       <c r="L132" t="s">
-        <v>3287</v>
+        <v>3286</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.2">
@@ -16900,7 +16593,7 @@
         <v>257</v>
       </c>
       <c r="B133" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="C133" s="5" t="s">
         <v>124</v>
@@ -16909,25 +16602,25 @@
         <v>255</v>
       </c>
       <c r="E133" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>gfx/Stairs_Up.positions</v>
       </c>
       <c r="F133" t="s">
         <v>256</v>
       </c>
       <c r="G133" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>47002</v>
       </c>
       <c r="H133" s="5">
         <v>116</v>
       </c>
       <c r="I133" s="6" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>74</v>
       </c>
       <c r="L133" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.2">
@@ -16935,7 +16628,7 @@
         <v>260</v>
       </c>
       <c r="B134" t="s">
-        <v>3289</v>
+        <v>3288</v>
       </c>
       <c r="C134" s="5" t="s">
         <v>124</v>
@@ -16944,25 +16637,25 @@
         <v>258</v>
       </c>
       <c r="E134" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>gfx/Stairs_Down.positions</v>
       </c>
       <c r="F134" t="s">
         <v>259</v>
       </c>
       <c r="G134" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>47118</v>
       </c>
       <c r="H134" s="5">
         <v>116</v>
       </c>
       <c r="I134" s="6" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>74</v>
       </c>
       <c r="L134" t="s">
-        <v>3289</v>
+        <v>3288</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.2">
@@ -16970,7 +16663,7 @@
         <v>263</v>
       </c>
       <c r="B135" t="s">
-        <v>3290</v>
+        <v>3289</v>
       </c>
       <c r="C135" s="5" t="s">
         <v>124</v>
@@ -16979,25 +16672,25 @@
         <v>261</v>
       </c>
       <c r="E135" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>gfx/Misc_Pillar.positions</v>
       </c>
       <c r="F135" t="s">
         <v>262</v>
       </c>
       <c r="G135" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>47234</v>
       </c>
       <c r="H135" s="5">
         <v>72</v>
       </c>
       <c r="I135" s="6" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>48</v>
       </c>
       <c r="L135" t="s">
-        <v>3290</v>
+        <v>3289</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.2">
@@ -17005,7 +16698,7 @@
         <v>266</v>
       </c>
       <c r="B136" t="s">
-        <v>3291</v>
+        <v>3290</v>
       </c>
       <c r="C136" s="5" t="s">
         <v>124</v>
@@ -17014,25 +16707,25 @@
         <v>264</v>
       </c>
       <c r="E136" t="str">
-        <f t="shared" ref="E136:E149" si="22">C136&amp;"/"&amp;D136</f>
+        <f t="shared" ref="E136:E149" si="25">C136&amp;"/"&amp;D136</f>
         <v>gfx/Door.Positions</v>
       </c>
       <c r="F136" t="s">
         <v>265</v>
       </c>
       <c r="G136" s="5">
-        <f t="shared" ref="G136:G149" si="23">IF(F136&lt;&gt;"",HEX2DEC(SUBSTITUTE(SUBSTITUTE(F136,"adrEA",""),"$","")),"")</f>
+        <f t="shared" ref="G136:G149" si="26">IF(F136&lt;&gt;"",HEX2DEC(SUBSTITUTE(SUBSTITUTE(F136,"adrEA",""),"$","")),"")</f>
         <v>47306</v>
       </c>
       <c r="H136" s="5">
         <v>80</v>
       </c>
       <c r="I136" s="6" t="str">
-        <f t="shared" ref="I136:I149" si="24">IFERROR(DEC2HEX(H136),"")</f>
+        <f t="shared" ref="I136:I149" si="27">IFERROR(DEC2HEX(H136),"")</f>
         <v>50</v>
       </c>
       <c r="L136" t="s">
-        <v>3291</v>
+        <v>3290</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.2">
@@ -17040,7 +16733,7 @@
         <v>269</v>
       </c>
       <c r="B137" t="s">
-        <v>3292</v>
+        <v>3291</v>
       </c>
       <c r="C137" s="5" t="s">
         <v>124</v>
@@ -17049,25 +16742,25 @@
         <v>267</v>
       </c>
       <c r="E137" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>gfx/Misc_Bed.positions</v>
       </c>
       <c r="F137" t="s">
         <v>268</v>
       </c>
       <c r="G137" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>47386</v>
       </c>
       <c r="H137" s="5">
         <v>72</v>
       </c>
       <c r="I137" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>48</v>
       </c>
       <c r="L137" t="s">
-        <v>3292</v>
+        <v>3291</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.2">
@@ -17075,7 +16768,7 @@
         <v>272</v>
       </c>
       <c r="B138" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="C138" s="5" t="s">
         <v>124</v>
@@ -17084,25 +16777,25 @@
         <v>270</v>
       </c>
       <c r="E138" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>gfx/Main_Shelf.positions</v>
       </c>
       <c r="F138" t="s">
         <v>271</v>
       </c>
       <c r="G138" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>47458</v>
       </c>
       <c r="H138" s="5">
         <v>112</v>
       </c>
       <c r="I138" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>70</v>
       </c>
       <c r="L138" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.2">
@@ -17110,7 +16803,7 @@
         <v>275</v>
       </c>
       <c r="B139" t="s">
-        <v>3294</v>
+        <v>3293</v>
       </c>
       <c r="C139" s="5" t="s">
         <v>124</v>
@@ -17119,25 +16812,25 @@
         <v>273</v>
       </c>
       <c r="E139" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>gfx/Main_Sign.positions</v>
       </c>
       <c r="F139" t="s">
         <v>274</v>
       </c>
       <c r="G139" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>47570</v>
       </c>
       <c r="H139" s="5">
         <v>112</v>
       </c>
       <c r="I139" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>70</v>
       </c>
       <c r="L139" t="s">
-        <v>3294</v>
+        <v>3293</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.2">
@@ -17145,7 +16838,7 @@
         <v>278</v>
       </c>
       <c r="B140" t="s">
-        <v>3295</v>
+        <v>3294</v>
       </c>
       <c r="C140" s="5" t="s">
         <v>124</v>
@@ -17154,25 +16847,25 @@
         <v>276</v>
       </c>
       <c r="E140" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>gfx/Main_SignOverlay.positions</v>
       </c>
       <c r="F140" t="s">
         <v>277</v>
       </c>
       <c r="G140" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>47682</v>
       </c>
       <c r="H140" s="5">
         <v>112</v>
       </c>
       <c r="I140" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>70</v>
       </c>
       <c r="L140" t="s">
-        <v>3295</v>
+        <v>3294</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.2">
@@ -17180,7 +16873,7 @@
         <v>281</v>
       </c>
       <c r="B141" t="s">
-        <v>3296</v>
+        <v>3295</v>
       </c>
       <c r="C141" s="5" t="s">
         <v>124</v>
@@ -17189,25 +16882,25 @@
         <v>279</v>
       </c>
       <c r="E141" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>gfx/Main_SignOverlay.offsets</v>
       </c>
       <c r="F141" t="s">
         <v>280</v>
       </c>
       <c r="G141" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>44800</v>
       </c>
       <c r="H141" s="5">
         <v>32</v>
       </c>
       <c r="I141" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>20</v>
       </c>
       <c r="L141" t="s">
-        <v>3296</v>
+        <v>3295</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.2">
@@ -17215,7 +16908,7 @@
         <v>284</v>
       </c>
       <c r="B142" t="s">
-        <v>3297</v>
+        <v>3296</v>
       </c>
       <c r="C142" s="5" t="s">
         <v>124</v>
@@ -17224,25 +16917,25 @@
         <v>282</v>
       </c>
       <c r="E142" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>gfx/Main_Slots.positions</v>
       </c>
       <c r="F142" t="s">
         <v>283</v>
       </c>
       <c r="G142" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>47794</v>
       </c>
       <c r="H142" s="5">
         <v>112</v>
       </c>
       <c r="I142" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>70</v>
       </c>
       <c r="L142" t="s">
-        <v>3297</v>
+        <v>3296</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.2">
@@ -17250,7 +16943,7 @@
         <v>287</v>
       </c>
       <c r="B143" t="s">
-        <v>3298</v>
+        <v>3297</v>
       </c>
       <c r="C143" s="5" t="s">
         <v>124</v>
@@ -17259,14 +16952,14 @@
         <v>285</v>
       </c>
       <c r="E143" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>gfx/Main_Switches.positions</v>
       </c>
       <c r="F143" t="s">
         <v>286</v>
       </c>
       <c r="G143" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>47906</v>
       </c>
       <c r="H143" s="5">
@@ -17277,7 +16970,7 @@
         <v>70</v>
       </c>
       <c r="L143" t="s">
-        <v>3298</v>
+        <v>3297</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.2">
@@ -17285,7 +16978,7 @@
         <v>290</v>
       </c>
       <c r="B144" t="s">
-        <v>3299</v>
+        <v>3298</v>
       </c>
       <c r="C144" s="5" t="s">
         <v>124</v>
@@ -17294,25 +16987,25 @@
         <v>288</v>
       </c>
       <c r="E144" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>gfx/Pad_Pit_Low.positions</v>
       </c>
       <c r="F144" t="s">
         <v>289</v>
       </c>
       <c r="G144" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>48018</v>
       </c>
       <c r="H144" s="5">
         <v>76</v>
       </c>
       <c r="I144" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>4C</v>
       </c>
       <c r="L144" t="s">
-        <v>3299</v>
+        <v>3298</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.2">
@@ -17320,7 +17013,7 @@
         <v>293</v>
       </c>
       <c r="B145" t="s">
-        <v>3300</v>
+        <v>3299</v>
       </c>
       <c r="C145" s="5" t="s">
         <v>124</v>
@@ -17329,25 +17022,25 @@
         <v>291</v>
       </c>
       <c r="E145" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>gfx/Pad_Trigger.positions</v>
       </c>
       <c r="F145" t="s">
         <v>292</v>
       </c>
       <c r="G145" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>48094</v>
       </c>
       <c r="H145" s="5">
         <v>76</v>
       </c>
       <c r="I145" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>4C</v>
       </c>
       <c r="L145" t="s">
-        <v>3300</v>
+        <v>3299</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.2">
@@ -17355,7 +17048,7 @@
         <v>296</v>
       </c>
       <c r="B146" t="s">
-        <v>3301</v>
+        <v>3300</v>
       </c>
       <c r="C146" s="5" t="s">
         <v>124</v>
@@ -17364,25 +17057,25 @@
         <v>294</v>
       </c>
       <c r="E146" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>gfx/Wooden_Doors.positions</v>
       </c>
       <c r="F146" t="s">
         <v>295</v>
       </c>
       <c r="G146" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>48170</v>
       </c>
       <c r="H146" s="5">
         <v>112</v>
       </c>
       <c r="I146" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>70</v>
       </c>
       <c r="L146" t="s">
-        <v>3301</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.2">
@@ -17390,7 +17083,7 @@
         <v>298</v>
       </c>
       <c r="B147" t="s">
-        <v>3302</v>
+        <v>3301</v>
       </c>
       <c r="C147" s="5" t="s">
         <v>124</v>
@@ -17399,25 +17092,25 @@
         <v>297</v>
       </c>
       <c r="E147" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>gfx/Main_Slots.offsets</v>
       </c>
       <c r="F147" t="s">
-        <v>3327</v>
+        <v>3318</v>
       </c>
       <c r="G147" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>44704</v>
       </c>
       <c r="H147" s="5">
         <v>32</v>
       </c>
       <c r="I147" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>20</v>
       </c>
       <c r="L147" t="s">
-        <v>3302</v>
+        <v>3301</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.2">
@@ -17434,21 +17127,21 @@
         <v>3195</v>
       </c>
       <c r="E148" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>gfx/Switches.colours</v>
       </c>
       <c r="F148" t="s">
-        <v>3328</v>
+        <v>3319</v>
       </c>
       <c r="G148" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>44736</v>
       </c>
       <c r="H148" s="5">
         <v>32</v>
       </c>
       <c r="I148" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>20</v>
       </c>
       <c r="L148" t="s">
@@ -17460,7 +17153,7 @@
         <v>300</v>
       </c>
       <c r="B149" t="s">
-        <v>3304</v>
+        <v>3303</v>
       </c>
       <c r="C149" s="5" t="s">
         <v>124</v>
@@ -17469,25 +17162,25 @@
         <v>3105</v>
       </c>
       <c r="E149" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>gfx/Main_Sign.colours</v>
       </c>
       <c r="F149" t="s">
-        <v>3329</v>
+        <v>3320</v>
       </c>
       <c r="G149" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>44768</v>
       </c>
       <c r="H149" s="5">
         <v>32</v>
       </c>
       <c r="I149" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>20</v>
       </c>
       <c r="L149" t="s">
-        <v>3304</v>
+        <v>3303</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.2">
@@ -17538,10 +17231,10 @@
         <v>monsters/Summon.gfx</v>
       </c>
       <c r="F152" t="s">
-        <v>3335</v>
+        <v>3326</v>
       </c>
       <c r="G152" s="5">
-        <f t="shared" ref="G152:G175" si="25">IF(F152&lt;&gt;"",HEX2DEC(SUBSTITUTE(SUBSTITUTE(F152,"adrEA",""),"$","")),"")</f>
+        <f t="shared" ref="G152:G175" si="28">IF(F152&lt;&gt;"",HEX2DEC(SUBSTITUTE(SUBSTITUTE(F152,"adrEA",""),"$","")),"")</f>
         <v>281748</v>
       </c>
       <c r="H152" s="5">
@@ -17569,17 +17262,17 @@
         <v>monsters/Behemoth.gfx</v>
       </c>
       <c r="F153" t="s">
-        <v>3336</v>
+        <v>3327</v>
       </c>
       <c r="G153" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>287564</v>
       </c>
       <c r="H153" s="5">
         <v>5096</v>
       </c>
       <c r="I153" s="6" t="str">
-        <f t="shared" ref="I153:I175" si="26">IFERROR(DEC2HEX(H153),"")</f>
+        <f t="shared" ref="I153:I175" si="29">IFERROR(DEC2HEX(H153),"")</f>
         <v>13E8</v>
       </c>
       <c r="K153">
@@ -17608,17 +17301,17 @@
         <v>monsters/Crab.gfx</v>
       </c>
       <c r="F154" t="s">
-        <v>3337</v>
+        <v>3328</v>
       </c>
       <c r="G154" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>292660</v>
       </c>
       <c r="H154" s="5">
         <v>1112</v>
       </c>
       <c r="I154" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>458</v>
       </c>
       <c r="K154">
@@ -17647,17 +17340,17 @@
         <v>monsters/CrabClaw.gfx</v>
       </c>
       <c r="F155" t="s">
-        <v>3338</v>
+        <v>3329</v>
       </c>
       <c r="G155" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>293772</v>
       </c>
       <c r="H155" s="5" t="s">
         <v>191</v>
       </c>
       <c r="I155" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>350</v>
       </c>
       <c r="K155">
@@ -17673,29 +17366,29 @@
         <v>2350</v>
       </c>
       <c r="B156" t="s">
-        <v>3585</v>
+        <v>3576</v>
       </c>
       <c r="C156" s="7" t="s">
         <v>51</v>
       </c>
       <c r="D156" t="s">
-        <v>3586</v>
+        <v>3577</v>
       </c>
       <c r="E156" t="s">
-        <v>3636</v>
+        <v>3627</v>
       </c>
       <c r="F156" t="s">
-        <v>3593</v>
+        <v>3584</v>
       </c>
       <c r="G156" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>40816</v>
       </c>
       <c r="H156" s="5">
         <v>12</v>
       </c>
       <c r="I156" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>C</v>
       </c>
       <c r="K156">
@@ -17711,29 +17404,29 @@
         <v>2351</v>
       </c>
       <c r="B157" t="s">
-        <v>3637</v>
+        <v>3628</v>
       </c>
       <c r="C157" s="7" t="s">
         <v>51</v>
       </c>
       <c r="D157" t="s">
-        <v>3638</v>
+        <v>3629</v>
       </c>
       <c r="E157" t="s">
-        <v>3639</v>
+        <v>3630</v>
       </c>
       <c r="F157" t="s">
-        <v>3594</v>
+        <v>3585</v>
       </c>
       <c r="G157" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>40828</v>
       </c>
       <c r="H157" s="5">
         <v>8</v>
       </c>
       <c r="I157" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>8</v>
       </c>
       <c r="L157" t="s">
@@ -17745,29 +17438,29 @@
         <v>2352</v>
       </c>
       <c r="B158" t="s">
-        <v>3587</v>
+        <v>3578</v>
       </c>
       <c r="C158" s="7" t="s">
         <v>51</v>
       </c>
       <c r="D158" t="s">
-        <v>3590</v>
+        <v>3581</v>
       </c>
       <c r="E158" t="s">
-        <v>3640</v>
+        <v>3631</v>
       </c>
       <c r="F158" t="s">
-        <v>3595</v>
+        <v>3586</v>
       </c>
       <c r="G158" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>40836</v>
       </c>
       <c r="H158" s="5">
         <v>32</v>
       </c>
       <c r="I158" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>20</v>
       </c>
     </row>
@@ -17776,29 +17469,29 @@
         <v>2353</v>
       </c>
       <c r="B159" t="s">
-        <v>3588</v>
+        <v>3579</v>
       </c>
       <c r="C159" s="7" t="s">
         <v>51</v>
       </c>
       <c r="D159" t="s">
-        <v>3589</v>
+        <v>3580</v>
       </c>
       <c r="E159" t="s">
-        <v>3641</v>
+        <v>3632</v>
       </c>
       <c r="F159" t="s">
-        <v>3596</v>
+        <v>3587</v>
       </c>
       <c r="G159" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>40868</v>
       </c>
       <c r="H159" s="5">
         <v>8</v>
       </c>
       <c r="I159" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>8</v>
       </c>
     </row>
@@ -17807,33 +17500,33 @@
         <v>2329</v>
       </c>
       <c r="B160" t="s">
-        <v>3597</v>
+        <v>3588</v>
       </c>
       <c r="C160" s="7" t="s">
         <v>51</v>
       </c>
       <c r="D160" t="s">
-        <v>3642</v>
+        <v>3633</v>
       </c>
       <c r="E160" t="s">
-        <v>3643</v>
+        <v>3634</v>
       </c>
       <c r="F160" t="s">
-        <v>3598</v>
+        <v>3589</v>
       </c>
       <c r="G160" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>40496</v>
       </c>
       <c r="H160" s="5">
         <v>4</v>
       </c>
       <c r="I160" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>4</v>
       </c>
       <c r="K160" t="s">
-        <v>3599</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="161" spans="1:13" x14ac:dyDescent="0.2">
@@ -17841,33 +17534,33 @@
         <v>2330</v>
       </c>
       <c r="B161" t="s">
-        <v>3644</v>
+        <v>3635</v>
       </c>
       <c r="C161" s="7" t="s">
         <v>51</v>
       </c>
       <c r="D161" t="s">
-        <v>3645</v>
+        <v>3636</v>
       </c>
       <c r="E161" t="s">
-        <v>3646</v>
+        <v>3637</v>
       </c>
       <c r="F161" t="s">
-        <v>3600</v>
+        <v>3591</v>
       </c>
       <c r="G161" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>40500</v>
       </c>
       <c r="H161" s="5">
         <v>4</v>
       </c>
       <c r="I161" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>4</v>
       </c>
       <c r="K161" t="s">
-        <v>3601</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="162" spans="1:13" x14ac:dyDescent="0.2">
@@ -17875,33 +17568,33 @@
         <v>2333</v>
       </c>
       <c r="B162" t="s">
-        <v>3602</v>
+        <v>3593</v>
       </c>
       <c r="C162" s="7" t="s">
         <v>51</v>
       </c>
       <c r="D162" t="s">
-        <v>3647</v>
+        <v>3638</v>
       </c>
       <c r="E162" t="s">
-        <v>3648</v>
+        <v>3639</v>
       </c>
       <c r="F162" t="s">
-        <v>3603</v>
+        <v>3594</v>
       </c>
       <c r="G162" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>40560</v>
       </c>
       <c r="H162" s="5">
         <v>4</v>
       </c>
       <c r="I162" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>4</v>
       </c>
       <c r="K162" t="s">
-        <v>3604</v>
+        <v>3595</v>
       </c>
     </row>
     <row r="163" spans="1:13" x14ac:dyDescent="0.2">
@@ -17909,33 +17602,33 @@
         <v>2334</v>
       </c>
       <c r="B163" t="s">
-        <v>3649</v>
+        <v>3640</v>
       </c>
       <c r="C163" s="7" t="s">
         <v>51</v>
       </c>
       <c r="D163" t="s">
-        <v>3650</v>
+        <v>3641</v>
       </c>
       <c r="E163" t="s">
-        <v>3651</v>
+        <v>3642</v>
       </c>
       <c r="F163" t="s">
-        <v>3605</v>
+        <v>3596</v>
       </c>
       <c r="G163" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>40564</v>
       </c>
       <c r="H163" s="5">
         <v>4</v>
       </c>
       <c r="I163" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>4</v>
       </c>
       <c r="K163" t="s">
-        <v>3606</v>
+        <v>3597</v>
       </c>
     </row>
     <row r="164" spans="1:13" x14ac:dyDescent="0.2">
@@ -17943,33 +17636,33 @@
         <v>2335</v>
       </c>
       <c r="B164" t="s">
-        <v>3652</v>
+        <v>3643</v>
       </c>
       <c r="C164" s="7" t="s">
         <v>51</v>
       </c>
       <c r="D164" t="s">
-        <v>3653</v>
+        <v>3644</v>
       </c>
       <c r="E164" t="s">
-        <v>3654</v>
+        <v>3645</v>
       </c>
       <c r="F164" t="s">
-        <v>3607</v>
+        <v>3598</v>
       </c>
       <c r="G164" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>40568</v>
       </c>
       <c r="H164" s="5">
         <v>4</v>
       </c>
       <c r="I164" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>4</v>
       </c>
       <c r="K164" t="s">
-        <v>3608</v>
+        <v>3599</v>
       </c>
     </row>
     <row r="165" spans="1:13" x14ac:dyDescent="0.2">
@@ -17977,33 +17670,33 @@
         <v>2337</v>
       </c>
       <c r="B165" t="s">
-        <v>3655</v>
+        <v>3646</v>
       </c>
       <c r="C165" s="7" t="s">
         <v>51</v>
       </c>
       <c r="D165" t="s">
-        <v>3656</v>
+        <v>3647</v>
       </c>
       <c r="E165" t="s">
-        <v>3657</v>
+        <v>3648</v>
       </c>
       <c r="F165" t="s">
-        <v>3609</v>
+        <v>3600</v>
       </c>
       <c r="G165" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>40606</v>
       </c>
       <c r="H165" s="5">
         <v>2</v>
       </c>
       <c r="I165" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>2</v>
       </c>
       <c r="K165" t="s">
-        <v>3610</v>
+        <v>3601</v>
       </c>
     </row>
     <row r="166" spans="1:13" x14ac:dyDescent="0.2">
@@ -18011,33 +17704,33 @@
         <v>2338</v>
       </c>
       <c r="B166" t="s">
-        <v>3658</v>
+        <v>3649</v>
       </c>
       <c r="C166" s="7" t="s">
         <v>51</v>
       </c>
       <c r="D166" t="s">
-        <v>3659</v>
+        <v>3650</v>
       </c>
       <c r="E166" t="s">
-        <v>3660</v>
+        <v>3651</v>
       </c>
       <c r="F166" t="s">
-        <v>3611</v>
+        <v>3602</v>
       </c>
       <c r="G166" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>40608</v>
       </c>
       <c r="H166" s="5">
         <v>2</v>
       </c>
       <c r="I166" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>2</v>
       </c>
       <c r="K166" t="s">
-        <v>3612</v>
+        <v>3603</v>
       </c>
     </row>
     <row r="167" spans="1:13" x14ac:dyDescent="0.2">
@@ -18045,33 +17738,33 @@
         <v>2341</v>
       </c>
       <c r="B167" t="s">
-        <v>3613</v>
+        <v>3604</v>
       </c>
       <c r="C167" s="7" t="s">
         <v>51</v>
       </c>
       <c r="D167" t="s">
-        <v>3661</v>
+        <v>3652</v>
       </c>
       <c r="E167" t="s">
-        <v>3662</v>
+        <v>3653</v>
       </c>
       <c r="F167" t="s">
-        <v>3614</v>
+        <v>3605</v>
       </c>
       <c r="G167" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>40660</v>
       </c>
       <c r="H167" s="5">
         <v>6</v>
       </c>
       <c r="I167" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>6</v>
       </c>
       <c r="K167" t="s">
-        <v>3615</v>
+        <v>3606</v>
       </c>
     </row>
     <row r="168" spans="1:13" x14ac:dyDescent="0.2">
@@ -18079,33 +17772,33 @@
         <v>2342</v>
       </c>
       <c r="B168" t="s">
-        <v>3663</v>
+        <v>3654</v>
       </c>
       <c r="C168" s="7" t="s">
         <v>51</v>
       </c>
       <c r="D168" t="s">
-        <v>3664</v>
+        <v>3655</v>
       </c>
       <c r="E168" t="s">
-        <v>3665</v>
+        <v>3656</v>
       </c>
       <c r="F168" t="s">
-        <v>3616</v>
+        <v>3607</v>
       </c>
       <c r="G168" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>40666</v>
       </c>
       <c r="H168" s="5">
         <v>6</v>
       </c>
       <c r="I168" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>6</v>
       </c>
       <c r="K168" t="s">
-        <v>3617</v>
+        <v>3608</v>
       </c>
     </row>
     <row r="169" spans="1:13" x14ac:dyDescent="0.2">
@@ -18113,33 +17806,33 @@
         <v>2343</v>
       </c>
       <c r="B169" t="s">
-        <v>3666</v>
+        <v>3657</v>
       </c>
       <c r="C169" s="7" t="s">
         <v>51</v>
       </c>
       <c r="D169" t="s">
-        <v>3667</v>
+        <v>3658</v>
       </c>
       <c r="E169" t="s">
-        <v>3668</v>
+        <v>3659</v>
       </c>
       <c r="F169" t="s">
-        <v>3618</v>
+        <v>3609</v>
       </c>
       <c r="G169" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>40672</v>
       </c>
       <c r="H169" s="5">
         <v>6</v>
       </c>
       <c r="I169" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>6</v>
       </c>
       <c r="K169" t="s">
-        <v>3619</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="170" spans="1:13" x14ac:dyDescent="0.2">
@@ -18147,33 +17840,33 @@
         <v>2344</v>
       </c>
       <c r="B170" t="s">
-        <v>3620</v>
+        <v>3611</v>
       </c>
       <c r="C170" s="7" t="s">
         <v>51</v>
       </c>
       <c r="D170" t="s">
-        <v>3669</v>
+        <v>3660</v>
       </c>
       <c r="E170" t="s">
-        <v>3670</v>
+        <v>3661</v>
       </c>
       <c r="F170" t="s">
-        <v>3621</v>
+        <v>3612</v>
       </c>
       <c r="G170" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>40678</v>
       </c>
       <c r="H170" s="5">
         <v>4</v>
       </c>
       <c r="I170" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>4</v>
       </c>
       <c r="K170" t="s">
-        <v>3622</v>
+        <v>3613</v>
       </c>
     </row>
     <row r="171" spans="1:13" x14ac:dyDescent="0.2">
@@ -18181,33 +17874,33 @@
         <v>2348</v>
       </c>
       <c r="B171" t="s">
-        <v>3671</v>
+        <v>3662</v>
       </c>
       <c r="C171" s="7" t="s">
         <v>51</v>
       </c>
       <c r="D171" t="s">
-        <v>3672</v>
+        <v>3663</v>
       </c>
       <c r="E171" t="s">
-        <v>3673</v>
+        <v>3664</v>
       </c>
       <c r="F171" t="s">
-        <v>3623</v>
+        <v>3614</v>
       </c>
       <c r="G171" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>40798</v>
       </c>
       <c r="H171" s="5">
         <v>2</v>
       </c>
       <c r="I171" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>2</v>
       </c>
       <c r="K171" t="s">
-        <v>3624</v>
+        <v>3615</v>
       </c>
     </row>
     <row r="172" spans="1:13" x14ac:dyDescent="0.2">
@@ -18215,33 +17908,33 @@
         <v>3123</v>
       </c>
       <c r="B172" t="s">
-        <v>3674</v>
+        <v>3665</v>
       </c>
       <c r="C172" s="7" t="s">
         <v>51</v>
       </c>
       <c r="D172" t="s">
-        <v>3675</v>
+        <v>3666</v>
       </c>
       <c r="E172" t="s">
-        <v>3680</v>
+        <v>3671</v>
       </c>
       <c r="F172" t="s">
-        <v>3339</v>
+        <v>3330</v>
       </c>
       <c r="G172" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>294620</v>
       </c>
       <c r="H172" s="5">
         <v>672</v>
       </c>
       <c r="I172" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>2A0</v>
       </c>
       <c r="J172" s="6" t="s">
-        <v>3676</v>
+        <v>3667</v>
       </c>
       <c r="L172" t="s">
         <v>3143</v>
@@ -18252,33 +17945,33 @@
         <v>3123</v>
       </c>
       <c r="B173" t="s">
-        <v>3678</v>
+        <v>3669</v>
       </c>
       <c r="C173" s="7" t="s">
         <v>51</v>
       </c>
       <c r="D173" t="s">
-        <v>3681</v>
+        <v>3672</v>
       </c>
       <c r="E173" t="s">
-        <v>3682</v>
+        <v>3673</v>
       </c>
       <c r="F173" t="s">
-        <v>3341</v>
+        <v>3332</v>
       </c>
       <c r="G173" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>295292</v>
       </c>
       <c r="H173" s="5">
         <v>160</v>
       </c>
       <c r="I173" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>A0</v>
       </c>
       <c r="J173" s="6" t="s">
-        <v>3683</v>
+        <v>3674</v>
       </c>
       <c r="L173" t="s">
         <v>3143</v>
@@ -18289,33 +17982,33 @@
         <v>3123</v>
       </c>
       <c r="B174" t="s">
-        <v>3679</v>
+        <v>3670</v>
       </c>
       <c r="C174" s="7" t="s">
         <v>51</v>
       </c>
       <c r="D174" t="s">
-        <v>3684</v>
+        <v>3675</v>
       </c>
       <c r="E174" t="s">
-        <v>3685</v>
+        <v>3676</v>
       </c>
       <c r="F174" t="s">
-        <v>3686</v>
+        <v>3677</v>
       </c>
       <c r="G174" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>295452</v>
       </c>
       <c r="H174" s="5">
         <v>864</v>
       </c>
       <c r="I174" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>360</v>
       </c>
       <c r="J174" s="6" t="s">
-        <v>3683</v>
+        <v>3674</v>
       </c>
       <c r="L174" t="s">
         <v>3143</v>
@@ -18326,33 +18019,33 @@
         <v>3123</v>
       </c>
       <c r="B175" t="s">
-        <v>3687</v>
+        <v>3678</v>
       </c>
       <c r="C175" s="7" t="s">
         <v>51</v>
       </c>
       <c r="D175" t="s">
-        <v>3688</v>
+        <v>3679</v>
       </c>
       <c r="E175" t="s">
-        <v>3689</v>
+        <v>3680</v>
       </c>
       <c r="F175" t="s">
-        <v>3592</v>
+        <v>3583</v>
       </c>
       <c r="G175" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>296316</v>
       </c>
       <c r="H175" s="5">
         <v>96</v>
       </c>
       <c r="I175" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>60</v>
       </c>
       <c r="J175" s="6" t="s">
-        <v>3683</v>
+        <v>3674</v>
       </c>
       <c r="L175" t="s">
         <v>3143</v>
@@ -18381,14 +18074,14 @@
       </c>
       <c r="C177" s="7"/>
       <c r="K177">
-        <f t="shared" ref="K177:K188" si="27">K176+H176</f>
+        <f t="shared" ref="K177:K188" si="30">K176+H176</f>
         <v>295292</v>
       </c>
       <c r="L177" t="s">
         <v>3147</v>
       </c>
       <c r="M177" t="str">
-        <f t="shared" ref="M177:M188" si="28">DEC2HEX(K177)</f>
+        <f t="shared" ref="M177:M188" si="31">DEC2HEX(K177)</f>
         <v>4817C</v>
       </c>
     </row>
@@ -18398,14 +18091,14 @@
       </c>
       <c r="C178" s="7"/>
       <c r="K178">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>295292</v>
       </c>
       <c r="L178" t="s">
         <v>3148</v>
       </c>
       <c r="M178" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>4817C</v>
       </c>
     </row>
@@ -18415,14 +18108,14 @@
       </c>
       <c r="C179" s="7"/>
       <c r="K179">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>295292</v>
       </c>
       <c r="L179" t="s">
         <v>3149</v>
       </c>
       <c r="M179" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>4817C</v>
       </c>
     </row>
@@ -18432,14 +18125,14 @@
       </c>
       <c r="C180" s="7"/>
       <c r="K180">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>295292</v>
       </c>
       <c r="L180" t="s">
         <v>3150</v>
       </c>
       <c r="M180" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>4817C</v>
       </c>
     </row>
@@ -18449,14 +18142,14 @@
       </c>
       <c r="C181" s="7"/>
       <c r="K181">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>295292</v>
       </c>
       <c r="L181" t="s">
         <v>3145</v>
       </c>
       <c r="M181" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>4817C</v>
       </c>
     </row>
@@ -18466,14 +18159,14 @@
       </c>
       <c r="C182" s="7"/>
       <c r="K182">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>295292</v>
       </c>
       <c r="L182" t="s">
         <v>3151</v>
       </c>
       <c r="M182" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>4817C</v>
       </c>
     </row>
@@ -18483,14 +18176,14 @@
       </c>
       <c r="C183" s="7"/>
       <c r="K183">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>295292</v>
       </c>
       <c r="L183" t="s">
         <v>3152</v>
       </c>
       <c r="M183" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>4817C</v>
       </c>
     </row>
@@ -18500,14 +18193,14 @@
       </c>
       <c r="C184" s="7"/>
       <c r="K184">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>295292</v>
       </c>
       <c r="L184" t="s">
         <v>3153</v>
       </c>
       <c r="M184" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>4817C</v>
       </c>
     </row>
@@ -18525,25 +18218,25 @@
         <v>192</v>
       </c>
       <c r="E185" t="str">
-        <f t="shared" ref="E185:E198" si="29">C185&amp;"/"&amp;D185</f>
+        <f t="shared" ref="E185:E198" si="32">C185&amp;"/"&amp;D185</f>
         <v>monsters/Dragon.gfx</v>
       </c>
       <c r="F185" t="s">
-        <v>3591</v>
+        <v>3582</v>
       </c>
       <c r="G185" s="5">
-        <f t="shared" ref="G185:G198" si="30">IF(F185&lt;&gt;"",HEX2DEC(SUBSTITUTE(SUBSTITUTE(F185,"adrEA",""),"$","")),"")</f>
+        <f t="shared" ref="G185:G198" si="33">IF(F185&lt;&gt;"",HEX2DEC(SUBSTITUTE(SUBSTITUTE(F185,"adrEA",""),"$","")),"")</f>
         <v>296412</v>
       </c>
       <c r="H185" s="5">
         <v>10544</v>
       </c>
       <c r="I185" s="6" t="str">
-        <f t="shared" ref="I185:I198" si="31">IFERROR(DEC2HEX(H185),"")</f>
+        <f t="shared" ref="I185:I198" si="34">IFERROR(DEC2HEX(H185),"")</f>
         <v>2930</v>
       </c>
       <c r="K185">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>295292</v>
       </c>
       <c r="L185" t="s">
@@ -18554,10 +18247,10 @@
         <v>4817C</v>
       </c>
       <c r="T185" s="15" t="s">
-        <v>3341</v>
+        <v>3332</v>
       </c>
       <c r="U185" t="s">
-        <v>3698</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.2">
@@ -18574,39 +18267,39 @@
         <v>193</v>
       </c>
       <c r="E186" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>monsters/Entropy.gfx</v>
       </c>
       <c r="F186" t="s">
-        <v>3699</v>
+        <v>3690</v>
       </c>
       <c r="G186" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>306956</v>
       </c>
       <c r="H186" s="5">
         <v>5234</v>
       </c>
       <c r="I186" s="6" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1472</v>
       </c>
       <c r="K186">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>305836</v>
       </c>
       <c r="L186" t="s">
         <v>3155</v>
       </c>
       <c r="M186" s="25" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>4AAAC</v>
       </c>
       <c r="T186" s="15" t="s">
-        <v>3697</v>
+        <v>3688</v>
       </c>
       <c r="U186" t="s">
-        <v>3698</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.2">
@@ -18627,7 +18320,7 @@
         <v>gfx/Pockets.gfx</v>
       </c>
       <c r="F187" t="s">
-        <v>3258</v>
+        <v>3257</v>
       </c>
       <c r="G187" s="5">
         <f>IF(F187&lt;&gt;"",HEX2DEC(SUBSTITUTE(SUBSTITUTE(F187,"adrEA",""),"$","")),"")</f>
@@ -18641,7 +18334,7 @@
         <v>7D20</v>
       </c>
       <c r="K187">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>311070</v>
       </c>
       <c r="L187" t="s">
@@ -18652,13 +18345,13 @@
         <v>312190</v>
       </c>
       <c r="O187" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="P187" s="21" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="R187" t="s">
-        <v>3257</v>
+        <v>3256</v>
       </c>
       <c r="S187" t="s">
         <v>3106</v>
@@ -18678,32 +18371,32 @@
         <v>196</v>
       </c>
       <c r="E188" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>sfx/sample1.sound</v>
       </c>
       <c r="F188" t="s">
         <v>197</v>
       </c>
       <c r="G188" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>344222</v>
       </c>
       <c r="H188" s="5">
         <v>132</v>
       </c>
       <c r="I188" s="6" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>84</v>
       </c>
       <c r="K188">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>343102</v>
       </c>
       <c r="L188" t="s">
         <v>3156</v>
       </c>
       <c r="M188" s="25" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>53C3E</v>
       </c>
     </row>
@@ -18765,21 +18458,21 @@
         <v>198</v>
       </c>
       <c r="E193" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>sfx/sample2.sound</v>
       </c>
       <c r="F193" t="s">
         <v>199</v>
       </c>
       <c r="G193" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>344354</v>
       </c>
       <c r="H193" s="5">
         <v>1474</v>
       </c>
       <c r="I193" s="6" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>5C2</v>
       </c>
       <c r="L193" t="s">
@@ -18800,21 +18493,21 @@
         <v>200</v>
       </c>
       <c r="E194" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>sfx/sample3.sound</v>
       </c>
       <c r="F194" t="s">
         <v>201</v>
       </c>
       <c r="G194" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>345828</v>
       </c>
       <c r="H194" s="5">
         <v>6280</v>
       </c>
       <c r="I194" s="6" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1888</v>
       </c>
       <c r="L194" t="s">
@@ -18835,21 +18528,21 @@
         <v>202</v>
       </c>
       <c r="E195" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>sfx/sample4.sound</v>
       </c>
       <c r="F195" t="s">
         <v>203</v>
       </c>
       <c r="G195" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>352108</v>
       </c>
       <c r="H195" s="5">
         <v>6070</v>
       </c>
       <c r="I195" s="6" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>17B6</v>
       </c>
       <c r="L195" t="s">
@@ -18870,21 +18563,21 @@
         <v>204</v>
       </c>
       <c r="E196" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>sfx/sample5.sound</v>
       </c>
       <c r="F196" t="s">
         <v>205</v>
       </c>
       <c r="G196" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>358178</v>
       </c>
       <c r="H196" s="5">
         <v>3458</v>
       </c>
       <c r="I196" s="6" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>D82</v>
       </c>
       <c r="L196" t="s">
@@ -18905,21 +18598,21 @@
         <v>206</v>
       </c>
       <c r="E197" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>data/reservespace1.block</v>
       </c>
       <c r="F197" t="s">
         <v>207</v>
       </c>
       <c r="G197" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>362636</v>
       </c>
       <c r="H197" s="5">
         <v>1000</v>
       </c>
       <c r="I197" s="6" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>3E8</v>
       </c>
       <c r="L197" t="s">
@@ -18940,21 +18633,21 @@
         <v>208</v>
       </c>
       <c r="E198" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>data/reservespace2.block</v>
       </c>
       <c r="F198" t="s">
         <v>209</v>
       </c>
       <c r="G198" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>361636</v>
       </c>
       <c r="H198" s="5">
         <v>1000</v>
       </c>
       <c r="I198" s="6" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>3E8</v>
       </c>
       <c r="L198" t="s">
@@ -22267,7 +21960,7 @@
         <v>MonsterAttackTypeTable</v>
       </c>
       <c r="L401" t="s">
-        <v>3377</v>
+        <v>3368</v>
       </c>
       <c r="M401" t="str">
         <f>IF(C401&lt;&gt;"",C401,_xlfn.XLOOKUP(B401,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -22283,7 +21976,7 @@
         <v>AttackType_DroneSpells</v>
       </c>
       <c r="L402" t="s">
-        <v>3381</v>
+        <v>3372</v>
       </c>
       <c r="M402" t="str">
         <f>IF(C402&lt;&gt;"",C402,_xlfn.XLOOKUP(B402,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -22302,28 +21995,28 @@
         <v>48</v>
       </c>
       <c r="D403" t="s">
-        <v>3350</v>
+        <v>3341</v>
       </c>
       <c r="E403" t="str">
-        <f t="shared" ref="E403" si="32">C403&amp;"/"&amp;D403</f>
+        <f t="shared" ref="E403" si="35">C403&amp;"/"&amp;D403</f>
         <v>data/monsters.spellbook.block</v>
       </c>
       <c r="F403" t="s">
-        <v>3349</v>
+        <v>3340</v>
       </c>
       <c r="G403" s="5">
-        <f t="shared" ref="G403" si="33">IF(F403&lt;&gt;"",HEX2DEC(SUBSTITUTE(SUBSTITUTE(F403,"adrEA",""),"$","")),"")</f>
+        <f t="shared" ref="G403" si="36">IF(F403&lt;&gt;"",HEX2DEC(SUBSTITUTE(SUBSTITUTE(F403,"adrEA",""),"$","")),"")</f>
         <v>4674</v>
       </c>
       <c r="H403" s="5">
         <v>16</v>
       </c>
       <c r="I403" s="6" t="str">
-        <f t="shared" ref="I403" si="34">IFERROR(DEC2HEX(H403),"")</f>
+        <f t="shared" ref="I403" si="37">IFERROR(DEC2HEX(H403),"")</f>
         <v>10</v>
       </c>
       <c r="L403" t="s">
-        <v>3348</v>
+        <v>3339</v>
       </c>
       <c r="M403" t="str">
         <f>IF(C403&lt;&gt;"",C403,_xlfn.XLOOKUP(B403,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -22339,7 +22032,7 @@
         <v>AttackType_Spells</v>
       </c>
       <c r="L404" t="s">
-        <v>3379</v>
+        <v>3370</v>
       </c>
       <c r="M404" t="str">
         <f>IF(C404&lt;&gt;"",C404,_xlfn.XLOOKUP(B404,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -22419,7 +22112,7 @@
         <v>AttackType_NoSpells</v>
       </c>
       <c r="L409" t="s">
-        <v>3378</v>
+        <v>3369</v>
       </c>
       <c r="M409" t="str">
         <f>IF(C409&lt;&gt;"",C409,_xlfn.XLOOKUP(B409,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -22435,7 +22128,7 @@
         <v>AttackType_ArcBoltMachine</v>
       </c>
       <c r="L410" t="s">
-        <v>3382</v>
+        <v>3373</v>
       </c>
       <c r="M410" t="str">
         <f>IF(C410&lt;&gt;"",C410,_xlfn.XLOOKUP(B410,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -22563,7 +22256,7 @@
         <v>AttackType_Drone</v>
       </c>
       <c r="L418" t="s">
-        <v>3380</v>
+        <v>3371</v>
       </c>
       <c r="M418" t="str">
         <f>IF(C418&lt;&gt;"",C418,_xlfn.XLOOKUP(B418,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -22691,7 +22384,7 @@
         <v>Monster_Movement_DataTable</v>
       </c>
       <c r="L426" t="s">
-        <v>3383</v>
+        <v>3374</v>
       </c>
       <c r="M426" t="str">
         <f>IF(C426&lt;&gt;"",C426,_xlfn.XLOOKUP(B426,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -24846,12 +24539,12 @@
       <c r="A561" t="s">
         <v>698</v>
       </c>
-      <c r="B561" t="str">
-        <f>IF(L561&lt;&gt;"",L561,_xlfn.XLOOKUP(A561,AI_NAMES!C:C,AI_NAMES!D:D,"",0))</f>
-        <v>.DropTheObject</v>
-      </c>
+      <c r="B561" s="27" t="s">
+        <v>3691</v>
+      </c>
+      <c r="C561" s="28"/>
       <c r="L561" t="s">
-        <v>3385</v>
+        <v>3376</v>
       </c>
       <c r="M561" t="str">
         <f>IF(C561&lt;&gt;"",C561,_xlfn.XLOOKUP(B561,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -24867,7 +24560,7 @@
         <v>DroppedObjects_DataTable</v>
       </c>
       <c r="L562" t="s">
-        <v>3384</v>
+        <v>3375</v>
       </c>
       <c r="M562" t="str">
         <f>IF(C562&lt;&gt;"",C562,_xlfn.XLOOKUP(B562,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -27139,7 +26832,7 @@
         <v>Trade_Exchange_TBC</v>
       </c>
       <c r="L704" t="s">
-        <v>3388</v>
+        <v>3379</v>
       </c>
       <c r="M704" t="str">
         <f>IF(C704&lt;&gt;"",C704,_xlfn.XLOOKUP(B704,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -27619,7 +27312,7 @@
         <v>ArmouryList</v>
       </c>
       <c r="L734" t="s">
-        <v>3387</v>
+        <v>3378</v>
       </c>
       <c r="M734" t="str">
         <f>IF(C734&lt;&gt;"",C734,_xlfn.XLOOKUP(B734,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -27651,7 +27344,7 @@
         <v>Trade_Offer_TBC</v>
       </c>
       <c r="L736" t="s">
-        <v>3389</v>
+        <v>3380</v>
       </c>
       <c r="M736" t="str">
         <f>IF(C736&lt;&gt;"",C736,_xlfn.XLOOKUP(B736,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -27683,7 +27376,7 @@
         <v>.Trader_NotPotionsButArms</v>
       </c>
       <c r="L738" t="s">
-        <v>3386</v>
+        <v>3377</v>
       </c>
       <c r="M738" t="str">
         <f>IF(C738&lt;&gt;"",C738,_xlfn.XLOOKUP(B738,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -27699,7 +27392,7 @@
         <v>.DontDivideList</v>
       </c>
       <c r="L739" t="s">
-        <v>3390</v>
+        <v>3381</v>
       </c>
       <c r="M739" t="str">
         <f>IF(C739&lt;&gt;"",C739,_xlfn.XLOOKUP(B739,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -35268,10 +34961,10 @@
         <v>1415</v>
       </c>
       <c r="B1219" t="s">
-        <v>3405</v>
+        <v>3396</v>
       </c>
       <c r="L1219" t="s">
-        <v>3405</v>
+        <v>3396</v>
       </c>
       <c r="M1219" t="str">
         <f>IF(C1219&lt;&gt;"",C1219,_xlfn.XLOOKUP(B1219,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -35283,10 +34976,10 @@
         <v>1416</v>
       </c>
       <c r="B1220" t="s">
-        <v>3392</v>
+        <v>3383</v>
       </c>
       <c r="L1220" t="s">
-        <v>3392</v>
+        <v>3383</v>
       </c>
       <c r="M1220" t="str">
         <f>IF(C1220&lt;&gt;"",C1220,_xlfn.XLOOKUP(B1220,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -38217,13 +37910,13 @@
         <v>1634</v>
       </c>
       <c r="B1416" t="s">
-        <v>3351</v>
+        <v>3342</v>
       </c>
       <c r="F1416">
         <v>16</v>
       </c>
       <c r="L1416" t="s">
-        <v>3351</v>
+        <v>3342</v>
       </c>
       <c r="M1416" t="str">
         <f>IF(C1416&lt;&gt;"",C1416,_xlfn.XLOOKUP(B1416,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -38520,10 +38213,10 @@
         <v>1660</v>
       </c>
       <c r="B1436" t="s">
-        <v>3399</v>
+        <v>3390</v>
       </c>
       <c r="L1436" t="s">
-        <v>3399</v>
+        <v>3390</v>
       </c>
       <c r="M1436" t="str">
         <f>IF(C1436&lt;&gt;"",C1436,_xlfn.XLOOKUP(B1436,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -38610,10 +38303,10 @@
         <v>1666</v>
       </c>
       <c r="B1442" t="s">
-        <v>3398</v>
+        <v>3389</v>
       </c>
       <c r="L1442" t="s">
-        <v>3398</v>
+        <v>3389</v>
       </c>
       <c r="M1442" t="str">
         <f>IF(C1442&lt;&gt;"",C1442,_xlfn.XLOOKUP(B1442,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -38640,10 +38333,10 @@
         <v>1668</v>
       </c>
       <c r="B1444" t="s">
-        <v>3394</v>
+        <v>3385</v>
       </c>
       <c r="L1444" t="s">
-        <v>3394</v>
+        <v>3385</v>
       </c>
       <c r="M1444" t="str">
         <f>IF(C1444&lt;&gt;"",C1444,_xlfn.XLOOKUP(B1444,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -38655,10 +38348,10 @@
         <v>1669</v>
       </c>
       <c r="B1445" t="s">
-        <v>3393</v>
+        <v>3384</v>
       </c>
       <c r="L1445" t="s">
-        <v>3393</v>
+        <v>3384</v>
       </c>
       <c r="M1445" t="str">
         <f>IF(C1445&lt;&gt;"",C1445,_xlfn.XLOOKUP(B1445,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -38730,10 +38423,10 @@
         <v>1674</v>
       </c>
       <c r="B1450" t="s">
-        <v>3397</v>
+        <v>3388</v>
       </c>
       <c r="L1450" t="s">
-        <v>3397</v>
+        <v>3388</v>
       </c>
       <c r="M1450" t="str">
         <f>IF(C1450&lt;&gt;"",C1450,_xlfn.XLOOKUP(B1450,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -38895,10 +38588,10 @@
         <v>1685</v>
       </c>
       <c r="B1461" t="s">
-        <v>3404</v>
+        <v>3395</v>
       </c>
       <c r="L1461" t="s">
-        <v>3404</v>
+        <v>3395</v>
       </c>
       <c r="M1461" t="str">
         <f>IF(C1461&lt;&gt;"",C1461,_xlfn.XLOOKUP(B1461,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -38955,10 +38648,10 @@
         <v>1689</v>
       </c>
       <c r="B1465" t="s">
-        <v>3395</v>
+        <v>3386</v>
       </c>
       <c r="L1465" t="s">
-        <v>3395</v>
+        <v>3386</v>
       </c>
       <c r="M1465" t="str">
         <f>IF(C1465&lt;&gt;"",C1465,_xlfn.XLOOKUP(B1465,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -38985,10 +38678,10 @@
         <v>1692</v>
       </c>
       <c r="B1467" t="s">
-        <v>3396</v>
+        <v>3387</v>
       </c>
       <c r="L1467" t="s">
-        <v>3396</v>
+        <v>3387</v>
       </c>
       <c r="M1467" t="str">
         <f>IF(C1467&lt;&gt;"",C1467,_xlfn.XLOOKUP(B1467,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -39210,10 +38903,10 @@
         <v>1707</v>
       </c>
       <c r="B1482" t="s">
-        <v>3402</v>
+        <v>3393</v>
       </c>
       <c r="L1482" t="s">
-        <v>3402</v>
+        <v>3393</v>
       </c>
       <c r="M1482" t="str">
         <f>IF(C1482&lt;&gt;"",C1482,_xlfn.XLOOKUP(B1482,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -39225,10 +38918,10 @@
         <v>1708</v>
       </c>
       <c r="B1483" t="s">
-        <v>3401</v>
+        <v>3392</v>
       </c>
       <c r="L1483" t="s">
-        <v>3401</v>
+        <v>3392</v>
       </c>
       <c r="M1483" t="str">
         <f>IF(C1483&lt;&gt;"",C1483,_xlfn.XLOOKUP(B1483,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -39240,10 +38933,10 @@
         <v>1709</v>
       </c>
       <c r="B1484" t="s">
-        <v>3400</v>
+        <v>3391</v>
       </c>
       <c r="L1484" t="s">
-        <v>3400</v>
+        <v>3391</v>
       </c>
       <c r="M1484" t="str">
         <f>IF(C1484&lt;&gt;"",C1484,_xlfn.XLOOKUP(B1484,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -39255,10 +38948,10 @@
         <v>1710</v>
       </c>
       <c r="B1485" t="s">
-        <v>3403</v>
+        <v>3394</v>
       </c>
       <c r="L1485" t="s">
-        <v>3403</v>
+        <v>3394</v>
       </c>
       <c r="M1485" t="str">
         <f>IF(C1485&lt;&gt;"",C1485,_xlfn.XLOOKUP(B1485,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -39270,10 +38963,10 @@
         <v>1711</v>
       </c>
       <c r="B1486" t="s">
-        <v>3406</v>
+        <v>3397</v>
       </c>
       <c r="L1486" t="s">
-        <v>3406</v>
+        <v>3397</v>
       </c>
       <c r="M1486" t="str">
         <f>IF(C1486&lt;&gt;"",C1486,_xlfn.XLOOKUP(B1486,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -39344,11 +39037,11 @@
       <c r="A1491" t="s">
         <v>1720</v>
       </c>
-      <c r="B1491" t="s">
-        <v>3434</v>
+      <c r="B1491" s="27" t="s">
+        <v>3692</v>
       </c>
       <c r="L1491" t="s">
-        <v>3434</v>
+        <v>3425</v>
       </c>
       <c r="M1491" t="str">
         <f>IF(C1491&lt;&gt;"",C1491,_xlfn.XLOOKUP(B1491,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -39359,11 +39052,11 @@
       <c r="A1492" t="s">
         <v>1721</v>
       </c>
-      <c r="B1492" t="s">
-        <v>3412</v>
+      <c r="B1492" s="27" t="s">
+        <v>3693</v>
       </c>
       <c r="L1492" t="s">
-        <v>3412</v>
+        <v>3403</v>
       </c>
       <c r="M1492" t="str">
         <f>IF(C1492&lt;&gt;"",C1492,_xlfn.XLOOKUP(B1492,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -39375,13 +39068,13 @@
         <v>1722</v>
       </c>
       <c r="B1493" t="s">
-        <v>3414</v>
+        <v>3405</v>
       </c>
       <c r="C1493" s="5" t="s">
-        <v>3413</v>
+        <v>3404</v>
       </c>
       <c r="L1493" t="s">
-        <v>3414</v>
+        <v>3405</v>
       </c>
       <c r="M1493" t="str">
         <f>IF(C1493&lt;&gt;"",C1493,_xlfn.XLOOKUP(B1493,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -39393,10 +39086,10 @@
         <v>1723</v>
       </c>
       <c r="B1494" t="s">
-        <v>3416</v>
+        <v>3407</v>
       </c>
       <c r="L1494" t="s">
-        <v>3416</v>
+        <v>3407</v>
       </c>
       <c r="M1494">
         <f>IF(C1494&lt;&gt;"",C1494,_xlfn.XLOOKUP(B1494,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -39408,10 +39101,10 @@
         <v>1724</v>
       </c>
       <c r="B1495" t="s">
-        <v>3417</v>
+        <v>3408</v>
       </c>
       <c r="L1495" t="s">
-        <v>3417</v>
+        <v>3408</v>
       </c>
       <c r="M1495">
         <f>IF(C1495&lt;&gt;"",C1495,_xlfn.XLOOKUP(B1495,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -39423,10 +39116,10 @@
         <v>1725</v>
       </c>
       <c r="B1496" t="s">
-        <v>3418</v>
+        <v>3409</v>
       </c>
       <c r="L1496" t="s">
-        <v>3418</v>
+        <v>3409</v>
       </c>
       <c r="M1496">
         <f>IF(C1496&lt;&gt;"",C1496,_xlfn.XLOOKUP(B1496,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -39438,10 +39131,10 @@
         <v>1726</v>
       </c>
       <c r="B1497" t="s">
-        <v>3419</v>
+        <v>3410</v>
       </c>
       <c r="L1497" t="s">
-        <v>3419</v>
+        <v>3410</v>
       </c>
       <c r="M1497">
         <f>IF(C1497&lt;&gt;"",C1497,_xlfn.XLOOKUP(B1497,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -39453,10 +39146,10 @@
         <v>1727</v>
       </c>
       <c r="B1498" t="s">
-        <v>3420</v>
+        <v>3411</v>
       </c>
       <c r="L1498" t="s">
-        <v>3420</v>
+        <v>3411</v>
       </c>
       <c r="M1498">
         <f>IF(C1498&lt;&gt;"",C1498,_xlfn.XLOOKUP(B1498,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -39468,10 +39161,10 @@
         <v>1728</v>
       </c>
       <c r="B1499" t="s">
-        <v>3421</v>
+        <v>3412</v>
       </c>
       <c r="L1499" t="s">
-        <v>3421</v>
+        <v>3412</v>
       </c>
       <c r="M1499">
         <f>IF(C1499&lt;&gt;"",C1499,_xlfn.XLOOKUP(B1499,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -39483,10 +39176,10 @@
         <v>1729</v>
       </c>
       <c r="B1500" t="s">
-        <v>3422</v>
+        <v>3413</v>
       </c>
       <c r="L1500" t="s">
-        <v>3422</v>
+        <v>3413</v>
       </c>
       <c r="M1500">
         <f>IF(C1500&lt;&gt;"",C1500,_xlfn.XLOOKUP(B1500,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -39498,10 +39191,10 @@
         <v>1730</v>
       </c>
       <c r="B1501" t="s">
-        <v>3423</v>
+        <v>3414</v>
       </c>
       <c r="L1501" t="s">
-        <v>3423</v>
+        <v>3414</v>
       </c>
       <c r="M1501">
         <f>IF(C1501&lt;&gt;"",C1501,_xlfn.XLOOKUP(B1501,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -39513,10 +39206,10 @@
         <v>1731</v>
       </c>
       <c r="B1502" t="s">
-        <v>3424</v>
+        <v>3415</v>
       </c>
       <c r="L1502" t="s">
-        <v>3424</v>
+        <v>3415</v>
       </c>
       <c r="M1502">
         <f>IF(C1502&lt;&gt;"",C1502,_xlfn.XLOOKUP(B1502,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -39558,10 +39251,10 @@
         <v>1736</v>
       </c>
       <c r="B1505" t="s">
-        <v>3415</v>
+        <v>3406</v>
       </c>
       <c r="L1505" t="s">
-        <v>3415</v>
+        <v>3406</v>
       </c>
       <c r="M1505" t="str">
         <f>IF(C1505&lt;&gt;"",C1505,_xlfn.XLOOKUP(B1505,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -39573,10 +39266,10 @@
         <v>1737</v>
       </c>
       <c r="B1506" t="s">
-        <v>3433</v>
+        <v>3424</v>
       </c>
       <c r="L1506" t="s">
-        <v>3433</v>
+        <v>3424</v>
       </c>
       <c r="M1506">
         <f>IF(C1506&lt;&gt;"",C1506,_xlfn.XLOOKUP(B1506,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -39588,10 +39281,10 @@
         <v>1738</v>
       </c>
       <c r="B1507" t="s">
-        <v>3432</v>
+        <v>3423</v>
       </c>
       <c r="L1507" t="s">
-        <v>3432</v>
+        <v>3423</v>
       </c>
       <c r="M1507">
         <f>IF(C1507&lt;&gt;"",C1507,_xlfn.XLOOKUP(B1507,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -39603,10 +39296,10 @@
         <v>1739</v>
       </c>
       <c r="B1508" t="s">
-        <v>3431</v>
+        <v>3422</v>
       </c>
       <c r="L1508" t="s">
-        <v>3431</v>
+        <v>3422</v>
       </c>
       <c r="M1508">
         <f>IF(C1508&lt;&gt;"",C1508,_xlfn.XLOOKUP(B1508,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -39618,10 +39311,10 @@
         <v>1740</v>
       </c>
       <c r="B1509" t="s">
-        <v>3430</v>
+        <v>3421</v>
       </c>
       <c r="L1509" t="s">
-        <v>3430</v>
+        <v>3421</v>
       </c>
       <c r="M1509">
         <f>IF(C1509&lt;&gt;"",C1509,_xlfn.XLOOKUP(B1509,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -39633,10 +39326,10 @@
         <v>1741</v>
       </c>
       <c r="B1510" t="s">
-        <v>3429</v>
+        <v>3420</v>
       </c>
       <c r="L1510" t="s">
-        <v>3429</v>
+        <v>3420</v>
       </c>
       <c r="M1510">
         <f>IF(C1510&lt;&gt;"",C1510,_xlfn.XLOOKUP(B1510,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -39648,10 +39341,10 @@
         <v>1742</v>
       </c>
       <c r="B1511" t="s">
-        <v>3428</v>
+        <v>3419</v>
       </c>
       <c r="L1511" t="s">
-        <v>3428</v>
+        <v>3419</v>
       </c>
       <c r="M1511">
         <f>IF(C1511&lt;&gt;"",C1511,_xlfn.XLOOKUP(B1511,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -39663,10 +39356,10 @@
         <v>1743</v>
       </c>
       <c r="B1512" t="s">
-        <v>3427</v>
+        <v>3418</v>
       </c>
       <c r="L1512" t="s">
-        <v>3427</v>
+        <v>3418</v>
       </c>
       <c r="M1512">
         <f>IF(C1512&lt;&gt;"",C1512,_xlfn.XLOOKUP(B1512,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -39678,10 +39371,10 @@
         <v>1744</v>
       </c>
       <c r="B1513" t="s">
-        <v>3426</v>
+        <v>3417</v>
       </c>
       <c r="L1513" t="s">
-        <v>3426</v>
+        <v>3417</v>
       </c>
       <c r="M1513">
         <f>IF(C1513&lt;&gt;"",C1513,_xlfn.XLOOKUP(B1513,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -39693,10 +39386,10 @@
         <v>1745</v>
       </c>
       <c r="B1514" t="s">
-        <v>3425</v>
+        <v>3416</v>
       </c>
       <c r="L1514" t="s">
-        <v>3425</v>
+        <v>3416</v>
       </c>
       <c r="M1514">
         <f>IF(C1514&lt;&gt;"",C1514,_xlfn.XLOOKUP(B1514,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -39738,10 +39431,10 @@
         <v>1750</v>
       </c>
       <c r="B1517" t="s">
-        <v>3443</v>
+        <v>3434</v>
       </c>
       <c r="L1517" t="s">
-        <v>3443</v>
+        <v>3434</v>
       </c>
       <c r="M1517" t="str">
         <f>IF(C1517&lt;&gt;"",C1517,_xlfn.XLOOKUP(B1517,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -39753,10 +39446,10 @@
         <v>1751</v>
       </c>
       <c r="B1518" t="s">
-        <v>3442</v>
+        <v>3433</v>
       </c>
       <c r="L1518" t="s">
-        <v>3442</v>
+        <v>3433</v>
       </c>
       <c r="M1518" t="str">
         <f>IF(C1518&lt;&gt;"",C1518,_xlfn.XLOOKUP(B1518,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -39792,10 +39485,10 @@
         <v>1756</v>
       </c>
       <c r="B1521" t="s">
-        <v>3441</v>
+        <v>3432</v>
       </c>
       <c r="L1521" t="s">
-        <v>3441</v>
+        <v>3432</v>
       </c>
       <c r="M1521" t="str">
         <f>IF(C1521&lt;&gt;"",C1521,_xlfn.XLOOKUP(B1521,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -39822,10 +39515,10 @@
         <v>1758</v>
       </c>
       <c r="B1523" t="s">
-        <v>3440</v>
+        <v>3431</v>
       </c>
       <c r="L1523" t="s">
-        <v>3440</v>
+        <v>3431</v>
       </c>
       <c r="M1523" t="str">
         <f>IF(C1523&lt;&gt;"",C1523,_xlfn.XLOOKUP(B1523,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -40017,10 +39710,10 @@
         <v>1775</v>
       </c>
       <c r="B1536" t="s">
-        <v>3439</v>
+        <v>3430</v>
       </c>
       <c r="L1536" t="s">
-        <v>3439</v>
+        <v>3430</v>
       </c>
       <c r="M1536" t="str">
         <f>IF(C1536&lt;&gt;"",C1536,_xlfn.XLOOKUP(B1536,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -40071,10 +39764,10 @@
         <v>1780</v>
       </c>
       <c r="B1540" t="s">
-        <v>3445</v>
+        <v>3436</v>
       </c>
       <c r="L1540" t="s">
-        <v>3445</v>
+        <v>3436</v>
       </c>
       <c r="M1540" t="str">
         <f>IF(C1540&lt;&gt;"",C1540,_xlfn.XLOOKUP(B1540,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -40101,10 +39794,10 @@
         <v>1782</v>
       </c>
       <c r="B1542" t="s">
-        <v>3447</v>
+        <v>3438</v>
       </c>
       <c r="L1542" t="s">
-        <v>3447</v>
+        <v>3438</v>
       </c>
       <c r="M1542" t="str">
         <f>IF(C1542&lt;&gt;"",C1542,_xlfn.XLOOKUP(B1542,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -40146,10 +39839,10 @@
         <v>1787</v>
       </c>
       <c r="B1545" t="s">
-        <v>3444</v>
+        <v>3435</v>
       </c>
       <c r="L1545" t="s">
-        <v>3444</v>
+        <v>3435</v>
       </c>
       <c r="M1545" t="str">
         <f>IF(C1545&lt;&gt;"",C1545,_xlfn.XLOOKUP(B1545,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -40221,10 +39914,10 @@
         <v>1794</v>
       </c>
       <c r="B1550" t="s">
-        <v>3453</v>
+        <v>3444</v>
       </c>
       <c r="L1550" t="s">
-        <v>3453</v>
+        <v>3444</v>
       </c>
       <c r="M1550" t="str">
         <f>IF(C1550&lt;&gt;"",C1550,_xlfn.XLOOKUP(B1550,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -40236,10 +39929,10 @@
         <v>1795</v>
       </c>
       <c r="B1551" t="s">
-        <v>3448</v>
+        <v>3439</v>
       </c>
       <c r="L1551" t="s">
-        <v>3448</v>
+        <v>3439</v>
       </c>
       <c r="M1551" t="str">
         <f>IF(C1551&lt;&gt;"",C1551,_xlfn.XLOOKUP(B1551,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -40251,10 +39944,10 @@
         <v>1796</v>
       </c>
       <c r="B1552" t="s">
-        <v>3449</v>
+        <v>3440</v>
       </c>
       <c r="L1552" t="s">
-        <v>3449</v>
+        <v>3440</v>
       </c>
       <c r="M1552" t="str">
         <f>IF(C1552&lt;&gt;"",C1552,_xlfn.XLOOKUP(B1552,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -40266,10 +39959,10 @@
         <v>1797</v>
       </c>
       <c r="B1553" t="s">
-        <v>3450</v>
+        <v>3441</v>
       </c>
       <c r="L1553" t="s">
-        <v>3450</v>
+        <v>3441</v>
       </c>
       <c r="M1553" t="str">
         <f>IF(C1553&lt;&gt;"",C1553,_xlfn.XLOOKUP(B1553,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -40281,10 +39974,10 @@
         <v>1798</v>
       </c>
       <c r="B1554" t="s">
-        <v>3451</v>
+        <v>3442</v>
       </c>
       <c r="L1554" t="s">
-        <v>3451</v>
+        <v>3442</v>
       </c>
       <c r="M1554" t="str">
         <f>IF(C1554&lt;&gt;"",C1554,_xlfn.XLOOKUP(B1554,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -40296,10 +39989,10 @@
         <v>1799</v>
       </c>
       <c r="B1555" t="s">
-        <v>3452</v>
+        <v>3443</v>
       </c>
       <c r="L1555" t="s">
-        <v>3452</v>
+        <v>3443</v>
       </c>
       <c r="M1555" t="str">
         <f>IF(C1555&lt;&gt;"",C1555,_xlfn.XLOOKUP(B1555,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -40311,10 +40004,10 @@
         <v>1800</v>
       </c>
       <c r="B1556" t="s">
-        <v>3446</v>
+        <v>3437</v>
       </c>
       <c r="L1556" t="s">
-        <v>3446</v>
+        <v>3437</v>
       </c>
       <c r="M1556" t="str">
         <f>IF(C1556&lt;&gt;"",C1556,_xlfn.XLOOKUP(B1556,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -40326,10 +40019,10 @@
         <v>1801</v>
       </c>
       <c r="B1557" t="s">
-        <v>3435</v>
+        <v>3426</v>
       </c>
       <c r="L1557" t="s">
-        <v>3435</v>
+        <v>3426</v>
       </c>
       <c r="M1557" t="str">
         <f>IF(C1557&lt;&gt;"",C1557,_xlfn.XLOOKUP(B1557,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -40341,10 +40034,10 @@
         <v>1802</v>
       </c>
       <c r="B1558" t="s">
-        <v>3436</v>
+        <v>3427</v>
       </c>
       <c r="L1558" t="s">
-        <v>3436</v>
+        <v>3427</v>
       </c>
       <c r="M1558" t="str">
         <f>IF(C1558&lt;&gt;"",C1558,_xlfn.XLOOKUP(B1558,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -40356,10 +40049,10 @@
         <v>1803</v>
       </c>
       <c r="B1559" t="s">
-        <v>3437</v>
+        <v>3428</v>
       </c>
       <c r="L1559" t="s">
-        <v>3437</v>
+        <v>3428</v>
       </c>
       <c r="M1559" t="str">
         <f>IF(C1559&lt;&gt;"",C1559,_xlfn.XLOOKUP(B1559,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -40566,10 +40259,10 @@
         <v>1817</v>
       </c>
       <c r="B1573" t="s">
-        <v>3438</v>
+        <v>3429</v>
       </c>
       <c r="L1573" t="s">
-        <v>3438</v>
+        <v>3429</v>
       </c>
       <c r="M1573" t="str">
         <f>IF(C1573&lt;&gt;"",C1573,_xlfn.XLOOKUP(B1573,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -40821,10 +40514,10 @@
         <v>1834</v>
       </c>
       <c r="B1590" t="s">
-        <v>3407</v>
+        <v>3398</v>
       </c>
       <c r="L1590" t="s">
-        <v>3407</v>
+        <v>3398</v>
       </c>
       <c r="M1590" t="str">
         <f>IF(C1590&lt;&gt;"",C1590,_xlfn.XLOOKUP(B1590,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -42186,10 +41879,10 @@
         <v>1925</v>
       </c>
       <c r="B1681" t="s">
-        <v>3411</v>
+        <v>3402</v>
       </c>
       <c r="L1681" t="s">
-        <v>3411</v>
+        <v>3402</v>
       </c>
       <c r="M1681" t="str">
         <f>IF(C1681&lt;&gt;"",C1681,_xlfn.XLOOKUP(B1681,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -44091,10 +43784,10 @@
         <v>2061</v>
       </c>
       <c r="B1808" t="s">
-        <v>3409</v>
+        <v>3400</v>
       </c>
       <c r="L1808" t="s">
-        <v>3409</v>
+        <v>3400</v>
       </c>
       <c r="M1808" t="str">
         <f>IF(C1808&lt;&gt;"",C1808,_xlfn.XLOOKUP(B1808,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -44106,10 +43799,10 @@
         <v>2062</v>
       </c>
       <c r="B1809" t="s">
-        <v>3408</v>
+        <v>3399</v>
       </c>
       <c r="L1809" t="s">
-        <v>3408</v>
+        <v>3399</v>
       </c>
       <c r="M1809" t="str">
         <f>IF(C1809&lt;&gt;"",C1809,_xlfn.XLOOKUP(B1809,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -45534,10 +45227,10 @@
         <v>2163</v>
       </c>
       <c r="B1905" t="s">
-        <v>3369</v>
+        <v>3360</v>
       </c>
       <c r="L1905" t="s">
-        <v>3369</v>
+        <v>3360</v>
       </c>
       <c r="M1905" t="str">
         <f>IF(C1905&lt;&gt;"",C1905,_xlfn.XLOOKUP(B1905,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -45564,10 +45257,10 @@
         <v>2165</v>
       </c>
       <c r="B1907" t="s">
-        <v>3363</v>
+        <v>3354</v>
       </c>
       <c r="L1907" t="s">
-        <v>3363</v>
+        <v>3354</v>
       </c>
       <c r="M1907" t="str">
         <f>IF(C1907&lt;&gt;"",C1907,_xlfn.XLOOKUP(B1907,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -45594,10 +45287,10 @@
         <v>2167</v>
       </c>
       <c r="B1909" t="s">
-        <v>3370</v>
+        <v>3361</v>
       </c>
       <c r="L1909" t="s">
-        <v>3370</v>
+        <v>3361</v>
       </c>
       <c r="M1909" t="str">
         <f>IF(C1909&lt;&gt;"",C1909,_xlfn.XLOOKUP(B1909,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -45939,10 +45632,10 @@
         <v>2190</v>
       </c>
       <c r="B1932" t="s">
-        <v>3332</v>
+        <v>3323</v>
       </c>
       <c r="L1932" t="s">
-        <v>3332</v>
+        <v>3323</v>
       </c>
       <c r="M1932" t="str">
         <f>IF(C1932&lt;&gt;"",C1932,_xlfn.XLOOKUP(B1932,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -45984,7 +45677,7 @@
         <v>2193</v>
       </c>
       <c r="C1935" s="5" t="s">
-        <v>3340</v>
+        <v>3331</v>
       </c>
       <c r="M1935" t="str">
         <f>IF(C1935&lt;&gt;"",C1935,_xlfn.XLOOKUP(B1935,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -46236,7 +45929,7 @@
         <v>2210</v>
       </c>
       <c r="B1952" t="s">
-        <v>3631</v>
+        <v>3622</v>
       </c>
       <c r="L1952" t="s">
         <v>321</v>
@@ -46611,7 +46304,7 @@
         <v>2237</v>
       </c>
       <c r="B1977" t="s">
-        <v>3632</v>
+        <v>3623</v>
       </c>
       <c r="M1977" t="str">
         <f>IF(C1977&lt;&gt;"",C1977,_xlfn.XLOOKUP(B1977,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -47025,10 +46718,10 @@
         <v>2271</v>
       </c>
       <c r="B2003" t="s">
-        <v>3354</v>
+        <v>3345</v>
       </c>
       <c r="L2003" t="s">
-        <v>3354</v>
+        <v>3345</v>
       </c>
       <c r="M2003" t="str">
         <f>IF(C2003&lt;&gt;"",C2003,_xlfn.XLOOKUP(B2003,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -47040,10 +46733,10 @@
         <v>2272</v>
       </c>
       <c r="B2004" t="s">
-        <v>3355</v>
+        <v>3346</v>
       </c>
       <c r="L2004" t="s">
-        <v>3355</v>
+        <v>3346</v>
       </c>
       <c r="M2004" t="str">
         <f>IF(C2004&lt;&gt;"",C2004,_xlfn.XLOOKUP(B2004,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -47430,10 +47123,10 @@
         <v>2300</v>
       </c>
       <c r="B2030" t="s">
-        <v>3361</v>
+        <v>3352</v>
       </c>
       <c r="L2030" t="s">
-        <v>3361</v>
+        <v>3352</v>
       </c>
       <c r="M2030" t="str">
         <f>IF(C2030&lt;&gt;"",C2030,_xlfn.XLOOKUP(B2030,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -47445,10 +47138,10 @@
         <v>2301</v>
       </c>
       <c r="B2031" t="s">
-        <v>3362</v>
+        <v>3353</v>
       </c>
       <c r="L2031" t="s">
-        <v>3362</v>
+        <v>3353</v>
       </c>
       <c r="M2031" t="str">
         <f>IF(C2031&lt;&gt;"",C2031,_xlfn.XLOOKUP(B2031,AI_NAMES!D:D,AI_NAMES!E:E,"",0))</f>
@@ -47610,7 +47303,7 @@
         <v>2312</v>
       </c>
       <c r="B2042" t="s">
-        <v>3635</v>
+        <v>3626</v>
       </c>
       <c r="L2042" t="s">
         <v>321</v>
@@ -47829,7 +47522,7 @@
         <v>2331</v>
       </c>
       <c r="B2057" t="s">
-        <v>3625</v>
+        <v>3616</v>
       </c>
       <c r="L2057" t="s">
         <v>321</v>
@@ -47856,7 +47549,7 @@
         <v>2336</v>
       </c>
       <c r="B2059" t="s">
-        <v>3626</v>
+        <v>3617</v>
       </c>
       <c r="L2059" t="s">
         <v>321</v>
@@ -47871,7 +47564,7 @@
         <v>2339</v>
       </c>
       <c r="B2060" t="s">
-        <v>3627</v>
+        <v>3618</v>
       </c>
       <c r="L2060" t="s">
         <v>321</v>
@@ -47890,7 +47583,7 @@
         <v>2345</v>
       </c>
       <c r="B2062" t="s">
-        <v>3628</v>
+        <v>3619</v>
       </c>
       <c r="L2062" t="s">
         <v>321</v>
@@ -47909,7 +47602,7 @@
         <v>2347</v>
       </c>
       <c r="B2064" t="s">
-        <v>3629</v>
+        <v>3620</v>
       </c>
       <c r="L2064" t="s">
         <v>321</v>
@@ -47920,7 +47613,7 @@
         <v>2349</v>
       </c>
       <c r="B2065" t="s">
-        <v>3630</v>
+        <v>3621</v>
       </c>
       <c r="L2065" t="s">
         <v>321</v>
@@ -47942,10 +47635,10 @@
         <v>2356</v>
       </c>
       <c r="B2067" t="s">
-        <v>3330</v>
+        <v>3321</v>
       </c>
       <c r="L2067" t="s">
-        <v>3330</v>
+        <v>3321</v>
       </c>
     </row>
     <row r="2068" spans="1:12" x14ac:dyDescent="0.2">
@@ -47953,10 +47646,10 @@
         <v>2357</v>
       </c>
       <c r="B2068" t="s">
-        <v>3331</v>
+        <v>3322</v>
       </c>
       <c r="L2068" t="s">
-        <v>3331</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="2069" spans="1:12" x14ac:dyDescent="0.2">
@@ -48357,20 +48050,20 @@
     </row>
     <row r="2105" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2105" t="s">
-        <v>3358</v>
+        <v>3349</v>
       </c>
       <c r="B2105" t="s">
-        <v>3359</v>
+        <v>3350</v>
       </c>
       <c r="H2105" s="5">
         <v>24</v>
       </c>
       <c r="I2105" s="6" t="str">
-        <f t="shared" ref="I2105" si="35">IFERROR(DEC2HEX(H2105),"")</f>
+        <f t="shared" ref="I2105" si="38">IFERROR(DEC2HEX(H2105),"")</f>
         <v>18</v>
       </c>
       <c r="L2105" t="s">
-        <v>3359</v>
+        <v>3350</v>
       </c>
     </row>
     <row r="2106" spans="1:12" x14ac:dyDescent="0.2">
@@ -48378,10 +48071,10 @@
         <v>2399</v>
       </c>
       <c r="B2106" t="s">
-        <v>3357</v>
+        <v>3348</v>
       </c>
       <c r="L2106" t="s">
-        <v>3357</v>
+        <v>3348</v>
       </c>
     </row>
     <row r="2107" spans="1:12" x14ac:dyDescent="0.2">
@@ -48389,10 +48082,10 @@
         <v>2400</v>
       </c>
       <c r="B2107" t="s">
-        <v>3360</v>
+        <v>3351</v>
       </c>
       <c r="L2107" t="s">
-        <v>3360</v>
+        <v>3351</v>
       </c>
     </row>
     <row r="2108" spans="1:12" x14ac:dyDescent="0.2">
@@ -48400,7 +48093,7 @@
         <v>2401</v>
       </c>
       <c r="B2108" t="s">
-        <v>3633</v>
+        <v>3624</v>
       </c>
       <c r="L2108" t="s">
         <v>321</v>
@@ -49041,7 +48734,7 @@
         <v>2463</v>
       </c>
       <c r="B2166" t="s">
-        <v>3634</v>
+        <v>3625</v>
       </c>
       <c r="L2166" t="s">
         <v>321</v>
@@ -49448,10 +49141,10 @@
         <v>2500</v>
       </c>
       <c r="B2203" t="s">
-        <v>3372</v>
+        <v>3363</v>
       </c>
       <c r="L2203" t="s">
-        <v>3372</v>
+        <v>3363</v>
       </c>
     </row>
     <row r="2204" spans="1:12" x14ac:dyDescent="0.2">
@@ -49470,10 +49163,10 @@
         <v>2502</v>
       </c>
       <c r="B2205" t="s">
-        <v>3374</v>
+        <v>3365</v>
       </c>
       <c r="L2205" t="s">
-        <v>3374</v>
+        <v>3365</v>
       </c>
     </row>
     <row r="2206" spans="1:12" x14ac:dyDescent="0.2">
@@ -49492,10 +49185,10 @@
         <v>2504</v>
       </c>
       <c r="B2207" t="s">
-        <v>3376</v>
+        <v>3367</v>
       </c>
       <c r="L2207" t="s">
-        <v>3376</v>
+        <v>3367</v>
       </c>
     </row>
     <row r="2208" spans="1:12" x14ac:dyDescent="0.2">
@@ -49514,10 +49207,10 @@
         <v>2506</v>
       </c>
       <c r="B2209" t="s">
-        <v>3375</v>
+        <v>3366</v>
       </c>
       <c r="L2209" t="s">
-        <v>3375</v>
+        <v>3366</v>
       </c>
     </row>
     <row r="2210" spans="1:12" x14ac:dyDescent="0.2">
@@ -49613,10 +49306,10 @@
         <v>2515</v>
       </c>
       <c r="B2218" t="s">
-        <v>3373</v>
+        <v>3364</v>
       </c>
       <c r="L2218" t="s">
-        <v>3373</v>
+        <v>3364</v>
       </c>
     </row>
     <row r="2219" spans="1:12" x14ac:dyDescent="0.2">
@@ -49635,7 +49328,7 @@
         <v>2517</v>
       </c>
       <c r="B2220" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
       <c r="C2220" s="5" t="s">
         <v>124</v>
@@ -49644,25 +49337,25 @@
         <v>3104</v>
       </c>
       <c r="E2220" t="str">
-        <f t="shared" ref="E2220" si="36">C2220&amp;"/"&amp;D2220</f>
+        <f t="shared" ref="E2220" si="39">C2220&amp;"/"&amp;D2220</f>
         <v>gfx/Main_Slots.colours</v>
       </c>
       <c r="F2220" t="s">
-        <v>3311</v>
+        <v>3310</v>
       </c>
       <c r="G2220" s="5">
-        <f t="shared" ref="G2220" si="37">IF(F2220&lt;&gt;"",HEX2DEC(SUBSTITUTE(SUBSTITUTE(F2220,"adrEA",""),"$","")),"")</f>
+        <f t="shared" ref="G2220" si="40">IF(F2220&lt;&gt;"",HEX2DEC(SUBSTITUTE(SUBSTITUTE(F2220,"adrEA",""),"$","")),"")</f>
         <v>44672</v>
       </c>
       <c r="H2220" s="5">
         <v>32</v>
       </c>
       <c r="I2220" s="6" t="str">
-        <f t="shared" ref="I2220" si="38">IFERROR(DEC2HEX(H2220),"")</f>
+        <f t="shared" ref="I2220" si="41">IFERROR(DEC2HEX(H2220),"")</f>
         <v>20</v>
       </c>
       <c r="L2220" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
     </row>
     <row r="2221" spans="1:12" x14ac:dyDescent="0.2">
@@ -49681,10 +49374,10 @@
         <v>2519</v>
       </c>
       <c r="B2222" t="s">
-        <v>3371</v>
+        <v>3362</v>
       </c>
       <c r="L2222" t="s">
-        <v>3371</v>
+        <v>3362</v>
       </c>
     </row>
     <row r="2223" spans="1:12" x14ac:dyDescent="0.2">
@@ -49692,34 +49385,34 @@
         <v>2520</v>
       </c>
       <c r="B2223" t="s">
-        <v>3342</v>
+        <v>3333</v>
       </c>
       <c r="C2223" s="5" t="s">
         <v>48</v>
       </c>
       <c r="D2223" t="s">
-        <v>3343</v>
+        <v>3334</v>
       </c>
       <c r="E2223" t="str">
-        <f t="shared" ref="E2223" si="39">C2223&amp;"/"&amp;D2223</f>
+        <f t="shared" ref="E2223" si="42">C2223&amp;"/"&amp;D2223</f>
         <v>data/Door_Lock.colours</v>
       </c>
       <c r="F2223" t="s">
-        <v>3344</v>
+        <v>3335</v>
       </c>
       <c r="G2223" s="5">
-        <f t="shared" ref="G2223" si="40">IF(F2223&lt;&gt;"",HEX2DEC(SUBSTITUTE(SUBSTITUTE(F2223,"adrEA",""),"$","")),"")</f>
+        <f t="shared" ref="G2223" si="43">IF(F2223&lt;&gt;"",HEX2DEC(SUBSTITUTE(SUBSTITUTE(F2223,"adrEA",""),"$","")),"")</f>
         <v>44882</v>
       </c>
       <c r="H2223" s="5">
         <v>8</v>
       </c>
       <c r="I2223" s="6" t="str">
-        <f t="shared" ref="I2223" si="41">IFERROR(DEC2HEX(H2223),"")</f>
+        <f t="shared" ref="I2223" si="44">IFERROR(DEC2HEX(H2223),"")</f>
         <v>8</v>
       </c>
       <c r="L2223" t="s">
-        <v>3342</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="2224" spans="1:12" x14ac:dyDescent="0.2">
@@ -49881,10 +49574,10 @@
         <v>2535</v>
       </c>
       <c r="B2238" t="s">
-        <v>3368</v>
+        <v>3359</v>
       </c>
       <c r="L2238" t="s">
-        <v>3368</v>
+        <v>3359</v>
       </c>
     </row>
     <row r="2239" spans="1:12" x14ac:dyDescent="0.2">
@@ -49892,10 +49585,10 @@
         <v>2536</v>
       </c>
       <c r="B2239" t="s">
-        <v>3391</v>
+        <v>3382</v>
       </c>
       <c r="L2239" t="s">
-        <v>3391</v>
+        <v>3382</v>
       </c>
     </row>
     <row r="2240" spans="1:12" x14ac:dyDescent="0.2">
@@ -49936,10 +49629,10 @@
         <v>2540</v>
       </c>
       <c r="B2243" t="s">
-        <v>3334</v>
+        <v>3325</v>
       </c>
       <c r="L2243" t="s">
-        <v>3334</v>
+        <v>3325</v>
       </c>
     </row>
     <row r="2244" spans="1:12" x14ac:dyDescent="0.2">
@@ -49947,10 +49640,10 @@
         <v>2541</v>
       </c>
       <c r="B2244" t="s">
-        <v>3333</v>
+        <v>3324</v>
       </c>
       <c r="L2244" t="s">
-        <v>3333</v>
+        <v>3324</v>
       </c>
     </row>
     <row r="2245" spans="1:12" x14ac:dyDescent="0.2">
@@ -49958,10 +49651,10 @@
         <v>2542</v>
       </c>
       <c r="B2245" t="s">
-        <v>3345</v>
+        <v>3336</v>
       </c>
       <c r="L2245" t="s">
-        <v>3345</v>
+        <v>3336</v>
       </c>
     </row>
     <row r="2246" spans="1:12" x14ac:dyDescent="0.2">
@@ -53317,10 +53010,10 @@
         <v>2922</v>
       </c>
       <c r="B2558" s="9" t="s">
-        <v>3364</v>
+        <v>3355</v>
       </c>
       <c r="L2558" t="s">
-        <v>3364</v>
+        <v>3355</v>
       </c>
     </row>
     <row r="2559" spans="1:12" x14ac:dyDescent="0.2">
@@ -53328,10 +53021,10 @@
         <v>2923</v>
       </c>
       <c r="B2559" s="9" t="s">
-        <v>3365</v>
+        <v>3356</v>
       </c>
       <c r="L2559" t="s">
-        <v>3365</v>
+        <v>3356</v>
       </c>
     </row>
     <row r="2560" spans="1:12" x14ac:dyDescent="0.2">
@@ -53339,10 +53032,10 @@
         <v>2924</v>
       </c>
       <c r="B2560" s="9" t="s">
-        <v>3366</v>
+        <v>3357</v>
       </c>
       <c r="L2560" t="s">
-        <v>3366</v>
+        <v>3357</v>
       </c>
     </row>
     <row r="2561" spans="1:12" x14ac:dyDescent="0.2">
@@ -53350,10 +53043,10 @@
         <v>2926</v>
       </c>
       <c r="B2561" t="s">
-        <v>3367</v>
+        <v>3358</v>
       </c>
       <c r="L2561" t="s">
-        <v>3367</v>
+        <v>3358</v>
       </c>
     </row>
     <row r="2562" spans="1:12" x14ac:dyDescent="0.2">
@@ -53383,10 +53076,10 @@
         <v>2929</v>
       </c>
       <c r="B2564" t="s">
-        <v>3410</v>
+        <v>3401</v>
       </c>
       <c r="L2564" t="s">
-        <v>3410</v>
+        <v>3401</v>
       </c>
     </row>
     <row r="2565" spans="1:12" x14ac:dyDescent="0.2">
@@ -53674,10 +53367,10 @@
         <v>2957</v>
       </c>
       <c r="B2591" t="s">
-        <v>3259</v>
+        <v>3258</v>
       </c>
       <c r="L2591" t="s">
-        <v>3259</v>
+        <v>3258</v>
       </c>
     </row>
     <row r="2592" spans="1:12" x14ac:dyDescent="0.2">
@@ -53707,10 +53400,10 @@
         <v>2960</v>
       </c>
       <c r="B2594" t="s">
-        <v>3261</v>
+        <v>3260</v>
       </c>
       <c r="L2594" t="s">
-        <v>3261</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="2595" spans="1:12" x14ac:dyDescent="0.2">
@@ -53850,10 +53543,10 @@
         <v>2973</v>
       </c>
       <c r="B2607" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
       <c r="L2607" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
     </row>
     <row r="2608" spans="1:12" x14ac:dyDescent="0.2">
@@ -53872,10 +53565,10 @@
         <v>2975</v>
       </c>
       <c r="B2609" t="s">
-        <v>3262</v>
+        <v>3261</v>
       </c>
       <c r="L2609" t="s">
-        <v>3262</v>
+        <v>3261</v>
       </c>
     </row>
     <row r="2610" spans="1:12" x14ac:dyDescent="0.2">
@@ -54030,18 +53723,18 @@
         <v>3000</v>
       </c>
       <c r="B2623" t="s">
-        <v>3356</v>
+        <v>3347</v>
       </c>
       <c r="H2623" s="5">
         <f>16*8*4</f>
         <v>512</v>
       </c>
       <c r="I2623" s="6" t="str">
-        <f t="shared" ref="I2623" si="42">IFERROR(DEC2HEX(H2623),"")</f>
+        <f t="shared" ref="I2623" si="45">IFERROR(DEC2HEX(H2623),"")</f>
         <v>200</v>
       </c>
       <c r="L2623" t="s">
-        <v>3356</v>
+        <v>3347</v>
       </c>
     </row>
     <row r="2624" spans="1:12" x14ac:dyDescent="0.2">
@@ -54313,26 +54006,28 @@
   <autoFilter ref="A1:O2647" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="A2:A1048576">
-    <cfRule type="expression" dxfId="9" priority="13">
+    <cfRule type="expression" dxfId="5" priority="13">
       <formula>AND(MATCH(A2,A:A,0)=ROW(A2),COUNTIF(A:A,A2)=1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="14">
+    <cfRule type="expression" dxfId="4" priority="14">
       <formula>AND(MATCH(A2,A:A,0)=ROW(A2),COUNTIF(A:A,A2)&gt;1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="17">
+    <cfRule type="expression" dxfId="3" priority="17">
       <formula>MATCH(A2,A:A,0)&lt;&gt;ROW(A2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B1048576">
-    <cfRule type="expression" dxfId="6" priority="5">
+    <cfRule type="expression" dxfId="2" priority="5">
       <formula>AND(B2&lt;&gt;"",_xlfn.ISFORMULA(B2)=TRUE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:L54 B55:I60 K55:L60 B61:L1048576">
-    <cfRule type="expression" dxfId="5" priority="6">
+  <conditionalFormatting sqref="B2:L54 B55:I60 B61:L1048576 K55:L60">
+    <cfRule type="expression" dxfId="1" priority="6">
       <formula>LEFT(LOWER($B2),7)="_delete"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="12">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:L54 B55:I60 K55:L60 B61:L1048576">
+    <cfRule type="expression" dxfId="0" priority="12">
       <formula>LEFT(LOWER($B2),7)="_offset"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54341,15 +54036,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5F6305C-6C97-FC48-B0B9-497181C42C64}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3E869A6-3675-A740-AFD9-6905E3EA45C5}">
   <dimension ref="A1:D205"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -54361,7 +54047,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>3454</v>
+        <v>3445</v>
       </c>
       <c r="B1">
         <f t="shared" ref="B1:B64" si="0">IFERROR(FIND(",",A1,1),"")</f>
@@ -54378,7 +54064,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>3455</v>
+        <v>3446</v>
       </c>
       <c r="B2">
         <f t="shared" si="0"/>
@@ -54395,7 +54081,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>3456</v>
+        <v>3447</v>
       </c>
       <c r="B3">
         <f t="shared" si="0"/>
@@ -54412,7 +54098,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>3457</v>
+        <v>3448</v>
       </c>
       <c r="B4">
         <f t="shared" si="0"/>
@@ -54429,7 +54115,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>3458</v>
+        <v>3449</v>
       </c>
       <c r="B5">
         <f t="shared" si="0"/>
@@ -54446,7 +54132,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>3459</v>
+        <v>3450</v>
       </c>
       <c r="B6">
         <f t="shared" si="0"/>
@@ -54463,7 +54149,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>3460</v>
+        <v>3451</v>
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
@@ -54480,7 +54166,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>3461</v>
+        <v>3452</v>
       </c>
       <c r="B8">
         <f t="shared" si="0"/>
@@ -54497,7 +54183,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>3462</v>
+        <v>3453</v>
       </c>
       <c r="B9">
         <f t="shared" si="0"/>
@@ -54514,7 +54200,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>3463</v>
+        <v>3454</v>
       </c>
       <c r="B10">
         <f t="shared" si="0"/>
@@ -54531,7 +54217,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>3464</v>
+        <v>3455</v>
       </c>
       <c r="B11">
         <f t="shared" si="0"/>
@@ -54548,7 +54234,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>3465</v>
+        <v>3456</v>
       </c>
       <c r="B12">
         <f t="shared" si="0"/>
@@ -54565,7 +54251,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>3466</v>
+        <v>3457</v>
       </c>
       <c r="B13">
         <f t="shared" si="0"/>
@@ -54582,7 +54268,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>3467</v>
+        <v>3458</v>
       </c>
       <c r="B14">
         <f t="shared" si="0"/>
@@ -54599,7 +54285,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>3468</v>
+        <v>3459</v>
       </c>
       <c r="B15">
         <f t="shared" si="0"/>
@@ -54616,7 +54302,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>3469</v>
+        <v>3460</v>
       </c>
       <c r="B16">
         <f t="shared" si="0"/>
@@ -54633,7 +54319,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>3470</v>
+        <v>3461</v>
       </c>
       <c r="B17">
         <f t="shared" si="0"/>
@@ -54650,7 +54336,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>3471</v>
+        <v>3462</v>
       </c>
       <c r="B18">
         <f t="shared" si="0"/>
@@ -54667,7 +54353,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>3472</v>
+        <v>3463</v>
       </c>
       <c r="B19">
         <f t="shared" si="0"/>
@@ -54684,7 +54370,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>3473</v>
+        <v>3464</v>
       </c>
       <c r="B20">
         <f t="shared" si="0"/>
@@ -54701,7 +54387,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>3474</v>
+        <v>3465</v>
       </c>
       <c r="B21">
         <f t="shared" si="0"/>
@@ -54718,7 +54404,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>3475</v>
+        <v>3466</v>
       </c>
       <c r="B22">
         <f t="shared" si="0"/>
@@ -54735,7 +54421,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>3476</v>
+        <v>3467</v>
       </c>
       <c r="B23">
         <f t="shared" si="0"/>
@@ -54752,7 +54438,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>3477</v>
+        <v>3468</v>
       </c>
       <c r="B24">
         <f t="shared" si="0"/>
@@ -54769,7 +54455,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>3478</v>
+        <v>3469</v>
       </c>
       <c r="B25">
         <f t="shared" si="0"/>
@@ -54786,7 +54472,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>3479</v>
+        <v>3470</v>
       </c>
       <c r="B26">
         <f t="shared" si="0"/>
@@ -54803,7 +54489,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>3480</v>
+        <v>3471</v>
       </c>
       <c r="B27">
         <f t="shared" si="0"/>
@@ -54820,7 +54506,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>3481</v>
+        <v>3472</v>
       </c>
       <c r="B28">
         <f t="shared" si="0"/>
@@ -54837,7 +54523,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>3482</v>
+        <v>3473</v>
       </c>
       <c r="B29">
         <f t="shared" si="0"/>
@@ -54854,7 +54540,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>3483</v>
+        <v>3474</v>
       </c>
       <c r="B30">
         <f t="shared" si="0"/>
@@ -54871,7 +54557,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>3484</v>
+        <v>3475</v>
       </c>
       <c r="B31">
         <f t="shared" si="0"/>
@@ -54888,7 +54574,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>3485</v>
+        <v>3476</v>
       </c>
       <c r="B32">
         <f t="shared" si="0"/>
@@ -54905,7 +54591,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>3486</v>
+        <v>3477</v>
       </c>
       <c r="B33">
         <f t="shared" si="0"/>
@@ -54922,7 +54608,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>3487</v>
+        <v>3478</v>
       </c>
       <c r="B34">
         <f t="shared" si="0"/>
@@ -54939,7 +54625,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>3488</v>
+        <v>3479</v>
       </c>
       <c r="B35">
         <f t="shared" si="0"/>
@@ -54956,7 +54642,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>3489</v>
+        <v>3480</v>
       </c>
       <c r="B36">
         <f t="shared" si="0"/>
@@ -54973,7 +54659,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>3490</v>
+        <v>3481</v>
       </c>
       <c r="B37">
         <f t="shared" si="0"/>
@@ -54990,7 +54676,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>3491</v>
+        <v>3482</v>
       </c>
       <c r="B38">
         <f t="shared" si="0"/>
@@ -55007,7 +54693,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>3492</v>
+        <v>3483</v>
       </c>
       <c r="B39">
         <f t="shared" si="0"/>
@@ -55024,7 +54710,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>3493</v>
+        <v>3484</v>
       </c>
       <c r="B40">
         <f t="shared" si="0"/>
@@ -55041,7 +54727,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>3494</v>
+        <v>3485</v>
       </c>
       <c r="B41">
         <f t="shared" si="0"/>
@@ -55058,7 +54744,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>3495</v>
+        <v>3486</v>
       </c>
       <c r="B42">
         <f t="shared" si="0"/>
@@ -55075,7 +54761,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>3496</v>
+        <v>3487</v>
       </c>
       <c r="B43">
         <f t="shared" si="0"/>
@@ -55092,7 +54778,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>3497</v>
+        <v>3488</v>
       </c>
       <c r="B44">
         <f t="shared" si="0"/>
@@ -55109,7 +54795,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>3498</v>
+        <v>3489</v>
       </c>
       <c r="B45">
         <f t="shared" si="0"/>
@@ -55126,7 +54812,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>3499</v>
+        <v>3490</v>
       </c>
       <c r="B46">
         <f t="shared" si="0"/>
@@ -55143,7 +54829,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>3500</v>
+        <v>3491</v>
       </c>
       <c r="B47">
         <f t="shared" si="0"/>
@@ -55160,7 +54846,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>3501</v>
+        <v>3492</v>
       </c>
       <c r="B48">
         <f t="shared" si="0"/>
@@ -55177,7 +54863,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>3502</v>
+        <v>3493</v>
       </c>
       <c r="B49">
         <f t="shared" si="0"/>
@@ -55194,7 +54880,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>3503</v>
+        <v>3494</v>
       </c>
       <c r="B50">
         <f t="shared" si="0"/>
@@ -55211,7 +54897,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>3504</v>
+        <v>3495</v>
       </c>
       <c r="B51">
         <f t="shared" si="0"/>
@@ -55228,7 +54914,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>3505</v>
+        <v>3496</v>
       </c>
       <c r="B52">
         <f t="shared" si="0"/>
@@ -55245,7 +54931,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>3506</v>
+        <v>3497</v>
       </c>
       <c r="B53">
         <f t="shared" si="0"/>
@@ -55262,7 +54948,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>3507</v>
+        <v>3498</v>
       </c>
       <c r="B54">
         <f t="shared" si="0"/>
@@ -55279,7 +54965,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>3508</v>
+        <v>3499</v>
       </c>
       <c r="B55">
         <f t="shared" si="0"/>
@@ -55296,7 +54982,7 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>3509</v>
+        <v>3500</v>
       </c>
       <c r="B56">
         <f t="shared" si="0"/>
@@ -55313,7 +54999,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>3510</v>
+        <v>3501</v>
       </c>
       <c r="B57">
         <f t="shared" si="0"/>
@@ -55330,7 +55016,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>3511</v>
+        <v>3502</v>
       </c>
       <c r="B58">
         <f t="shared" si="0"/>
@@ -55347,7 +55033,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>3538</v>
+        <v>3529</v>
       </c>
       <c r="B59">
         <f t="shared" si="0"/>
@@ -55364,7 +55050,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>3539</v>
+        <v>3530</v>
       </c>
       <c r="B60">
         <f t="shared" si="0"/>
@@ -55381,7 +55067,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>3540</v>
+        <v>3531</v>
       </c>
       <c r="B61">
         <f t="shared" si="0"/>
@@ -55398,7 +55084,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>3541</v>
+        <v>3532</v>
       </c>
       <c r="B62">
         <f t="shared" si="0"/>
@@ -55415,7 +55101,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>3542</v>
+        <v>3533</v>
       </c>
       <c r="B63">
         <f t="shared" si="0"/>
@@ -55432,7 +55118,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>3543</v>
+        <v>3534</v>
       </c>
       <c r="B64">
         <f t="shared" si="0"/>
@@ -55449,7 +55135,7 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>3544</v>
+        <v>3535</v>
       </c>
       <c r="B65">
         <f t="shared" ref="B65:B101" si="3">IFERROR(FIND(",",A65,1),"")</f>
@@ -55466,7 +55152,7 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>3545</v>
+        <v>3536</v>
       </c>
       <c r="B66">
         <f t="shared" si="3"/>
@@ -55483,7 +55169,7 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>3546</v>
+        <v>3537</v>
       </c>
       <c r="B67">
         <f t="shared" si="3"/>
@@ -55500,7 +55186,7 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>3547</v>
+        <v>3538</v>
       </c>
       <c r="B68">
         <f t="shared" si="3"/>
@@ -55517,7 +55203,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>3512</v>
+        <v>3503</v>
       </c>
       <c r="B69">
         <f t="shared" si="3"/>
@@ -55534,7 +55220,7 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>3513</v>
+        <v>3504</v>
       </c>
       <c r="B70">
         <f t="shared" si="3"/>
@@ -55551,7 +55237,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>3514</v>
+        <v>3505</v>
       </c>
       <c r="B71">
         <f t="shared" si="3"/>
@@ -55568,7 +55254,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>3515</v>
+        <v>3506</v>
       </c>
       <c r="B72">
         <f t="shared" si="3"/>
@@ -55585,7 +55271,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>3516</v>
+        <v>3507</v>
       </c>
       <c r="B73">
         <f t="shared" si="3"/>
@@ -55602,7 +55288,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>3517</v>
+        <v>3508</v>
       </c>
       <c r="B74">
         <f t="shared" si="3"/>
@@ -55619,7 +55305,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>3518</v>
+        <v>3509</v>
       </c>
       <c r="B75">
         <f t="shared" si="3"/>
@@ -55636,7 +55322,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>3519</v>
+        <v>3510</v>
       </c>
       <c r="B76">
         <f t="shared" si="3"/>
@@ -55653,7 +55339,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>3520</v>
+        <v>3511</v>
       </c>
       <c r="B77">
         <f t="shared" si="3"/>
@@ -55670,7 +55356,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>3521</v>
+        <v>3512</v>
       </c>
       <c r="B78">
         <f t="shared" si="3"/>
@@ -55687,7 +55373,7 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>3522</v>
+        <v>3513</v>
       </c>
       <c r="B79">
         <f t="shared" si="3"/>
@@ -55704,7 +55390,7 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>3523</v>
+        <v>3514</v>
       </c>
       <c r="B80">
         <f t="shared" si="3"/>
@@ -55721,7 +55407,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>3524</v>
+        <v>3515</v>
       </c>
       <c r="B81">
         <f t="shared" si="3"/>
@@ -55738,7 +55424,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>3525</v>
+        <v>3516</v>
       </c>
       <c r="B82">
         <f t="shared" si="3"/>
@@ -55755,7 +55441,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>3526</v>
+        <v>3517</v>
       </c>
       <c r="B83">
         <f t="shared" si="3"/>
@@ -55772,7 +55458,7 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>3527</v>
+        <v>3518</v>
       </c>
       <c r="B84">
         <f t="shared" si="3"/>
@@ -55789,7 +55475,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>3528</v>
+        <v>3519</v>
       </c>
       <c r="B85">
         <f t="shared" si="3"/>
@@ -55806,7 +55492,7 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>3529</v>
+        <v>3520</v>
       </c>
       <c r="B86">
         <f t="shared" si="3"/>
@@ -55823,7 +55509,7 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>3530</v>
+        <v>3521</v>
       </c>
       <c r="B87">
         <f t="shared" si="3"/>
@@ -55840,7 +55526,7 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>3531</v>
+        <v>3522</v>
       </c>
       <c r="B88">
         <f t="shared" si="3"/>
@@ -55857,7 +55543,7 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>3532</v>
+        <v>3523</v>
       </c>
       <c r="B89">
         <f t="shared" si="3"/>
@@ -55874,7 +55560,7 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>3533</v>
+        <v>3524</v>
       </c>
       <c r="B90">
         <f t="shared" si="3"/>
@@ -55891,7 +55577,7 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>3534</v>
+        <v>3525</v>
       </c>
       <c r="B91">
         <f t="shared" si="3"/>
@@ -55908,7 +55594,7 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>3535</v>
+        <v>3526</v>
       </c>
       <c r="B92">
         <f t="shared" si="3"/>
@@ -55925,7 +55611,7 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>3536</v>
+        <v>3527</v>
       </c>
       <c r="B93">
         <f t="shared" si="3"/>
@@ -55942,7 +55628,7 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>3537</v>
+        <v>3528</v>
       </c>
       <c r="B94">
         <f t="shared" si="3"/>
@@ -55959,7 +55645,7 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>3548</v>
+        <v>3539</v>
       </c>
       <c r="B95">
         <f t="shared" si="3"/>
@@ -55976,7 +55662,7 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>3549</v>
+        <v>3540</v>
       </c>
       <c r="B96">
         <f t="shared" si="3"/>
@@ -55993,7 +55679,7 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>3550</v>
+        <v>3541</v>
       </c>
       <c r="B97">
         <f t="shared" si="3"/>
@@ -56010,7 +55696,7 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>3551</v>
+        <v>3542</v>
       </c>
       <c r="B98">
         <f t="shared" si="3"/>
@@ -56027,7 +55713,7 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>3567</v>
+        <v>3558</v>
       </c>
       <c r="B99">
         <f t="shared" si="3"/>
@@ -56044,7 +55730,7 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>3566</v>
+        <v>3557</v>
       </c>
       <c r="B100">
         <f t="shared" si="3"/>
@@ -56061,7 +55747,7 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>3552</v>
+        <v>3543</v>
       </c>
       <c r="B101">
         <f t="shared" si="3"/>
@@ -56078,7 +55764,7 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>3568</v>
+        <v>3559</v>
       </c>
       <c r="B102">
         <f t="shared" ref="B102:B127" si="6">IFERROR(FIND(",",A102,1),"")</f>
@@ -56095,7 +55781,7 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>3569</v>
+        <v>3560</v>
       </c>
       <c r="B103">
         <f t="shared" si="6"/>
@@ -56112,7 +55798,7 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>3570</v>
+        <v>3561</v>
       </c>
       <c r="B104">
         <f t="shared" si="6"/>
@@ -56129,7 +55815,7 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>3571</v>
+        <v>3562</v>
       </c>
       <c r="B105">
         <f t="shared" si="6"/>
@@ -56146,7 +55832,7 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>3572</v>
+        <v>3563</v>
       </c>
       <c r="B106">
         <f t="shared" si="6"/>
@@ -56163,7 +55849,7 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>3573</v>
+        <v>3564</v>
       </c>
       <c r="B107">
         <f t="shared" si="6"/>
@@ -56180,7 +55866,7 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>3574</v>
+        <v>3565</v>
       </c>
       <c r="B108">
         <f t="shared" si="6"/>
@@ -56197,7 +55883,7 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>3575</v>
+        <v>3566</v>
       </c>
       <c r="B109">
         <f t="shared" si="6"/>
@@ -56214,7 +55900,7 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>3576</v>
+        <v>3567</v>
       </c>
       <c r="B110">
         <f t="shared" si="6"/>
@@ -56231,7 +55917,7 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>3577</v>
+        <v>3568</v>
       </c>
       <c r="B111">
         <f t="shared" si="6"/>
@@ -56248,7 +55934,7 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>3578</v>
+        <v>3569</v>
       </c>
       <c r="B112">
         <f t="shared" si="6"/>
@@ -56265,7 +55951,7 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>3579</v>
+        <v>3570</v>
       </c>
       <c r="B113">
         <f t="shared" si="6"/>
@@ -56282,7 +55968,7 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>3580</v>
+        <v>3571</v>
       </c>
       <c r="B114">
         <f t="shared" si="6"/>
@@ -56299,7 +55985,7 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>3581</v>
+        <v>3572</v>
       </c>
       <c r="B115">
         <f t="shared" si="6"/>
@@ -56316,7 +56002,7 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>3582</v>
+        <v>3573</v>
       </c>
       <c r="B116">
         <f t="shared" si="6"/>
@@ -56333,7 +56019,7 @@
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>3583</v>
+        <v>3574</v>
       </c>
       <c r="B117">
         <f t="shared" si="6"/>
@@ -56350,7 +56036,7 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>3584</v>
+        <v>3575</v>
       </c>
       <c r="B118">
         <f t="shared" si="6"/>

--- a/segments.xlsx
+++ b/segments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dom.cresswell/Dropbox/Geek/Gaming Projects/Bloodwych 68k/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADD68388-4CF4-C749-BD3E-EF9941A14933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE34092-C3AE-DF40-9D20-9041A28DC93A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="400" yWindow="880" windowWidth="29460" windowHeight="21620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3720" yWindow="880" windowWidth="29460" windowHeight="21620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BLOODWYCH439" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7748" uniqueCount="3834">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7797" uniqueCount="3882">
   <si>
     <t>Type</t>
   </si>
@@ -11539,6 +11539,150 @@
   </si>
   <si>
     <t>Offsets for the Crab body, face, front, back, and side components across Crab.gfx and CrabClaw.gfx.</t>
+  </si>
+  <si>
+    <t>Character_BodyDefinitions</t>
+  </si>
+  <si>
+    <t>characters-body-definitions.layout</t>
+  </si>
+  <si>
+    <t>$A50A</t>
+  </si>
+  <si>
+    <t>8C</t>
+  </si>
+  <si>
+    <t>Character_PartFacingVariants</t>
+  </si>
+  <si>
+    <t>characters-part-variants.lookup</t>
+  </si>
+  <si>
+    <t>data/characters-part-variants.lookup</t>
+  </si>
+  <si>
+    <t>$A600</t>
+  </si>
+  <si>
+    <t>Character_RenderTableOffsets</t>
+  </si>
+  <si>
+    <t>characters-render-table-offsets.lookup</t>
+  </si>
+  <si>
+    <t>data/characters-render-table-offsets.lookup</t>
+  </si>
+  <si>
+    <t>$A5EC</t>
+  </si>
+  <si>
+    <t>Character_ArmAnimationPositions</t>
+  </si>
+  <si>
+    <t>characters-arm-animation.positions</t>
+  </si>
+  <si>
+    <t>data/characters-arm-animation.positions</t>
+  </si>
+  <si>
+    <t>$A778</t>
+  </si>
+  <si>
+    <t>Character_RenderLayout_Standard</t>
+  </si>
+  <si>
+    <t>characters-standard-render.layout</t>
+  </si>
+  <si>
+    <t>data/characters-standard-render.layout</t>
+  </si>
+  <si>
+    <t>$18480</t>
+  </si>
+  <si>
+    <t>Character_Distant4_Positions_Standard</t>
+  </si>
+  <si>
+    <t>characters-standard-distant-4.positions</t>
+  </si>
+  <si>
+    <t>data/characters-standard-distant-4.positions</t>
+  </si>
+  <si>
+    <t>$185B0</t>
+  </si>
+  <si>
+    <t>Character_Distant5_Positions_Standard</t>
+  </si>
+  <si>
+    <t>characters-standard-distant-5.positions</t>
+  </si>
+  <si>
+    <t>data/characters-standard-distant-5.positions</t>
+  </si>
+  <si>
+    <t>$185B8</t>
+  </si>
+  <si>
+    <t>Character_RenderLayout_Alternate</t>
+  </si>
+  <si>
+    <t>characters-alternate-render.layout</t>
+  </si>
+  <si>
+    <t>data/characters-alternate-render.layout</t>
+  </si>
+  <si>
+    <t>$185C0</t>
+  </si>
+  <si>
+    <t>Character_Distant4_Positions_Alternate</t>
+  </si>
+  <si>
+    <t>characters-alternate-distant-4.positions</t>
+  </si>
+  <si>
+    <t>data/characters-alternate-distant-4.positions</t>
+  </si>
+  <si>
+    <t>$186F0</t>
+  </si>
+  <si>
+    <t>Character_Distant5_Positions_Alternate</t>
+  </si>
+  <si>
+    <t>characters-alternate-distant-5.positions</t>
+  </si>
+  <si>
+    <t>data/characters-alternate-distant-5.positions</t>
+  </si>
+  <si>
+    <t>$186F8</t>
+  </si>
+  <si>
+    <t>Draw_CharacterComponent</t>
+  </si>
+  <si>
+    <t>Fourteen 10-byte records containing a layout selector and BodyParts.gfx bases for legs, torso, arms and the distant composite.</t>
+  </si>
+  <si>
+    <t>Four signed XY pairs for the corresponding distant graphics slot.</t>
+  </si>
+  <si>
+    <t>Standard and alternate animated-arm Y corrections and facing-specific X corrections.</t>
+  </si>
+  <si>
+    <t>Five parts × four facings; bit 7 means mirror and $FF suppresses that part.</t>
+  </si>
+  <si>
+    <t>Interleaved five-entry lookup containing the height-table and graphics-source-table offsets for each rendered character part.</t>
+  </si>
+  <si>
+    <t>_Offset_Character_RenderTableOffsets_0x02</t>
+  </si>
+  <si>
+    <t>Draws one character component by selecting its distance, facing and animation variant, resolving its height and graphics source, applying its colour mask, and positioning or mirroring the 16-pixel strip.</t>
   </si>
 </sst>
 </file>
@@ -11719,7 +11863,64 @@
     <cellStyle name="Excel Built-in Normal" xfId="1" xr:uid="{ACE51F02-8306-284E-B6CB-6CB2D79D3F1F}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="3" tint="0.24994659260841701"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.749961851863155"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="5" tint="-0.24994659260841701"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color theme="3" tint="0.24994659260841701"/>
@@ -12117,7 +12318,8 @@
     <col min="5" max="5" width="61.5" customWidth="1"/>
     <col min="6" max="6" width="19.5" customWidth="1"/>
     <col min="7" max="8" width="10.83203125" style="5" customWidth="1"/>
-    <col min="9" max="10" width="14.83203125" style="6" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" style="6" customWidth="1"/>
+    <col min="10" max="10" width="26.83203125" style="6" customWidth="1"/>
     <col min="11" max="11" width="103.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="14.83203125" style="6" customWidth="1"/>
     <col min="14" max="15" width="70.83203125" customWidth="1"/>
@@ -19502,7 +19704,7 @@
         <v>3813</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>3342</v>
       </c>
@@ -19531,7 +19733,7 @@
       <c r="J210" s="6" t="s">
         <v>3657</v>
       </c>
-      <c r="K210" t="s">
+      <c r="K210" s="26" t="s">
         <v>3814</v>
       </c>
     </row>
@@ -57233,76 +57435,143 @@
         <v>321</v>
       </c>
     </row>
-    <row r="2134" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2134" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A2134" t="s">
         <v>2419</v>
       </c>
-      <c r="B2134" t="s">
-        <v>321</v>
+      <c r="B2134" s="26" t="s">
+        <v>3834</v>
+      </c>
+      <c r="C2134" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2134" s="26" t="s">
+        <v>3835</v>
       </c>
       <c r="E2134" t="str">
         <f t="shared" si="64"/>
-        <v/>
+        <v>data/characters-body-definitions.layout</v>
+      </c>
+      <c r="F2134" t="s">
+        <v>3836</v>
+      </c>
+      <c r="G2134">
+        <v>42250</v>
+      </c>
+      <c r="H2134">
+        <v>140</v>
+      </c>
+      <c r="I2134" s="26" t="s">
+        <v>3837</v>
+      </c>
+      <c r="K2134" s="6" t="s">
+        <v>3875</v>
       </c>
       <c r="O2134" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="2135" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2135" t="s">
+    <row r="2135" spans="1:15" ht="17" x14ac:dyDescent="0.25">
+      <c r="A2135" s="26" t="s">
         <v>2421</v>
       </c>
-      <c r="B2135" t="s">
-        <v>321</v>
-      </c>
-      <c r="E2135" t="str">
-        <f t="shared" si="64"/>
-        <v/>
+      <c r="B2135" s="26" t="s">
+        <v>3842</v>
+      </c>
+      <c r="C2135" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2135" s="26" t="s">
+        <v>3843</v>
+      </c>
+      <c r="E2135" s="26" t="s">
+        <v>3844</v>
+      </c>
+      <c r="F2135" t="s">
+        <v>3845</v>
+      </c>
+      <c r="G2135">
+        <v>42476</v>
+      </c>
+      <c r="H2135">
+        <v>20</v>
+      </c>
+      <c r="I2135" s="26">
+        <v>14</v>
+      </c>
+      <c r="J2135"/>
+      <c r="K2135" t="s">
+        <v>3879</v>
       </c>
       <c r="O2135" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="2136" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2136" t="s">
+    <row r="2136" spans="1:15" ht="17" x14ac:dyDescent="0.25">
+      <c r="A2136" s="26" t="s">
         <v>2422</v>
       </c>
-      <c r="B2136" t="s">
-        <v>321</v>
-      </c>
-      <c r="E2136" t="str">
-        <f t="shared" si="64"/>
-        <v/>
-      </c>
+      <c r="B2136" s="26" t="s">
+        <v>3880</v>
+      </c>
+      <c r="C2136"/>
+      <c r="G2136"/>
+      <c r="H2136"/>
+      <c r="I2136"/>
+      <c r="J2136"/>
+      <c r="K2136"/>
       <c r="O2136" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="2137" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2137" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A2137" t="s">
         <v>2423</v>
       </c>
-      <c r="B2137" t="s">
-        <v>321</v>
-      </c>
-      <c r="E2137" t="str">
-        <f t="shared" si="64"/>
-        <v/>
+      <c r="B2137" s="26" t="s">
+        <v>3838</v>
+      </c>
+      <c r="C2137" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2137" s="26" t="s">
+        <v>3839</v>
+      </c>
+      <c r="E2137" s="26" t="s">
+        <v>3840</v>
+      </c>
+      <c r="F2137" t="s">
+        <v>3841</v>
+      </c>
+      <c r="G2137">
+        <v>42496</v>
+      </c>
+      <c r="H2137">
+        <v>20</v>
+      </c>
+      <c r="I2137" s="26">
+        <v>14</v>
+      </c>
+      <c r="K2137" s="6" t="s">
+        <v>3878</v>
       </c>
       <c r="O2137" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="2138" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2138" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A2138" t="s">
         <v>2424</v>
       </c>
-      <c r="B2138" t="s">
-        <v>321</v>
+      <c r="B2138" s="26" t="s">
+        <v>3874</v>
       </c>
       <c r="E2138" t="str">
         <f t="shared" si="64"/>
         <v/>
+      </c>
+      <c r="K2138" s="6" t="s">
+        <v>3881</v>
       </c>
       <c r="O2138" t="s">
         <v>321</v>
@@ -57518,16 +57787,36 @@
         <v>321</v>
       </c>
     </row>
-    <row r="2153" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2153" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A2153" t="s">
         <v>2439</v>
       </c>
-      <c r="B2153" t="s">
-        <v>321</v>
-      </c>
-      <c r="E2153" t="str">
-        <f t="shared" si="64"/>
-        <v/>
+      <c r="B2153" s="26" t="s">
+        <v>3846</v>
+      </c>
+      <c r="C2153" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2153" s="26" t="s">
+        <v>3847</v>
+      </c>
+      <c r="E2153" s="26" t="s">
+        <v>3848</v>
+      </c>
+      <c r="F2153" t="s">
+        <v>3849</v>
+      </c>
+      <c r="G2153">
+        <v>42872</v>
+      </c>
+      <c r="H2153">
+        <v>72</v>
+      </c>
+      <c r="I2153" s="26">
+        <v>48</v>
+      </c>
+      <c r="K2153" s="6" t="s">
+        <v>3877</v>
       </c>
       <c r="O2153" t="s">
         <v>321</v>
@@ -64809,91 +65098,205 @@
         <v>3198</v>
       </c>
     </row>
-    <row r="2642" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2642" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A2642" t="s">
         <v>3017</v>
       </c>
-      <c r="B2642" t="s">
-        <v>321</v>
-      </c>
-      <c r="E2642" t="str">
-        <f t="shared" si="77"/>
-        <v/>
+      <c r="B2642" s="26" t="s">
+        <v>3850</v>
+      </c>
+      <c r="C2642" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2642" s="26" t="s">
+        <v>3851</v>
+      </c>
+      <c r="E2642" s="26" t="s">
+        <v>3852</v>
+      </c>
+      <c r="F2642" s="26" t="s">
+        <v>3853</v>
+      </c>
+      <c r="G2642">
+        <v>99456</v>
+      </c>
+      <c r="H2642">
+        <v>304</v>
+      </c>
+      <c r="I2642" s="26">
+        <v>130</v>
       </c>
       <c r="O2642" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="2643" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2643" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A2643" t="s">
         <v>3018</v>
       </c>
-      <c r="B2643" t="s">
-        <v>321</v>
-      </c>
-      <c r="E2643" t="str">
-        <f t="shared" si="77"/>
-        <v/>
+      <c r="B2643" s="26" t="s">
+        <v>3854</v>
+      </c>
+      <c r="C2643" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2643" s="26" t="s">
+        <v>3855</v>
+      </c>
+      <c r="E2643" s="26" t="s">
+        <v>3856</v>
+      </c>
+      <c r="F2643" s="26" t="s">
+        <v>3857</v>
+      </c>
+      <c r="G2643">
+        <v>99760</v>
+      </c>
+      <c r="H2643">
+        <v>8</v>
+      </c>
+      <c r="I2643" s="26">
+        <v>8</v>
+      </c>
+      <c r="K2643" s="6" t="s">
+        <v>3876</v>
       </c>
       <c r="O2643" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="2644" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2644" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A2644" t="s">
         <v>3019</v>
       </c>
-      <c r="B2644" t="s">
-        <v>321</v>
-      </c>
-      <c r="E2644" t="str">
-        <f t="shared" si="77"/>
-        <v/>
+      <c r="B2644" s="26" t="s">
+        <v>3858</v>
+      </c>
+      <c r="C2644" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2644" s="26" t="s">
+        <v>3859</v>
+      </c>
+      <c r="E2644" s="26" t="s">
+        <v>3860</v>
+      </c>
+      <c r="F2644" s="26" t="s">
+        <v>3861</v>
+      </c>
+      <c r="G2644">
+        <v>99768</v>
+      </c>
+      <c r="H2644">
+        <v>8</v>
+      </c>
+      <c r="I2644" s="26">
+        <v>8</v>
+      </c>
+      <c r="K2644" s="6" t="s">
+        <v>3876</v>
       </c>
       <c r="O2644" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="2645" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2645" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A2645" t="s">
         <v>3020</v>
       </c>
-      <c r="B2645" t="s">
-        <v>321</v>
-      </c>
-      <c r="E2645" t="str">
-        <f t="shared" si="77"/>
-        <v/>
+      <c r="B2645" s="26" t="s">
+        <v>3862</v>
+      </c>
+      <c r="C2645" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2645" s="26" t="s">
+        <v>3863</v>
+      </c>
+      <c r="E2645" s="26" t="s">
+        <v>3864</v>
+      </c>
+      <c r="F2645" s="26" t="s">
+        <v>3865</v>
+      </c>
+      <c r="G2645">
+        <v>99776</v>
+      </c>
+      <c r="H2645">
+        <v>304</v>
+      </c>
+      <c r="I2645" s="26">
+        <v>130</v>
       </c>
       <c r="O2645" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="2646" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2646" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A2646" t="s">
         <v>3021</v>
       </c>
-      <c r="B2646" t="s">
-        <v>321</v>
-      </c>
-      <c r="E2646" t="str">
-        <f t="shared" si="77"/>
-        <v/>
+      <c r="B2646" s="26" t="s">
+        <v>3866</v>
+      </c>
+      <c r="C2646" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2646" s="26" t="s">
+        <v>3867</v>
+      </c>
+      <c r="E2646" s="26" t="s">
+        <v>3868</v>
+      </c>
+      <c r="F2646" s="26" t="s">
+        <v>3869</v>
+      </c>
+      <c r="G2646">
+        <v>100080</v>
+      </c>
+      <c r="H2646">
+        <v>8</v>
+      </c>
+      <c r="I2646" s="26">
+        <v>8</v>
+      </c>
+      <c r="K2646" s="6" t="s">
+        <v>3876</v>
       </c>
       <c r="O2646" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="2647" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2647" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A2647" t="s">
         <v>3022</v>
       </c>
-      <c r="B2647" t="s">
-        <v>321</v>
-      </c>
-      <c r="E2647" t="str">
-        <f t="shared" si="77"/>
-        <v/>
+      <c r="B2647" s="26" t="s">
+        <v>3870</v>
+      </c>
+      <c r="C2647" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2647" s="26" t="s">
+        <v>3871</v>
+      </c>
+      <c r="E2647" s="26" t="s">
+        <v>3872</v>
+      </c>
+      <c r="F2647" s="26" t="s">
+        <v>3873</v>
+      </c>
+      <c r="G2647">
+        <v>100088</v>
+      </c>
+      <c r="H2647">
+        <v>8</v>
+      </c>
+      <c r="I2647" s="26">
+        <v>8</v>
+      </c>
+      <c r="K2647" s="6" t="s">
+        <v>3876</v>
       </c>
       <c r="O2647" t="s">
         <v>321</v>
@@ -64974,30 +65377,28 @@
   </sheetData>
   <autoFilter ref="A1:R2651" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="A2:A2651 A2695:A1048576">
-    <cfRule type="expression" dxfId="5" priority="13">
-      <formula>AND(MATCH(A2,A:A,0)=ROW(A2),COUNTIF(A:A,A2)=1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="14">
-      <formula>AND(MATCH(A2,A:A,0)=ROW(A2),COUNTIF(A:A,A2)&gt;1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="17">
-      <formula>MATCH(A2,A:A,0)&lt;&gt;ROW(A2)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B200 B2695:B1048576 B205:B218 B221:B222 B229:B2651">
-    <cfRule type="expression" dxfId="2" priority="5">
+  <conditionalFormatting sqref="B2:B9998">
+    <cfRule type="expression" dxfId="5" priority="5">
       <formula>AND(B2&lt;&gt;"",_xlfn.ISFORMULA(B2)=TRUE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2695:O1048576 N55:O60 B193:D199 B188:B192 D188:D190 B200 D200:D202 B176:D187 B2:O36 F37:O54 F55:I60 B37:E175 B205:D218 F61:O187 E176:E2651 C203:C204 B221:D222 C219:C220 B229:D2651 C223:C228 F230:O2651 F188:J229 L188:O229">
-    <cfRule type="expression" dxfId="1" priority="6">
+  <conditionalFormatting sqref="B2:Z9998">
+    <cfRule type="expression" dxfId="4" priority="6">
       <formula>LEFT(LOWER($B2),7)="_delete"</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="3" priority="12">
+      <formula>LEFT(LOWER($B2),7)="_offset"</formula>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N55:O60 B2695:O1048576 B193:D199 B188:B192 D188:D190 B200 D200:D202 B176:D187 B2:O36 F37:O54 F55:I60 B37:E175 B205:D218 F61:O187 E176:E2651 C203:C204 B221:D222 C219:C220 B229:D2651 C223:C228 F230:O2651 F188:J229 L188:O229">
-    <cfRule type="expression" dxfId="0" priority="12">
-      <formula>LEFT(LOWER($B2),7)="_offset"</formula>
+  <conditionalFormatting sqref="A2:A9998">
+    <cfRule type="expression" dxfId="2" priority="13">
+      <formula>AND(MATCH(A2,A:A,0)=ROW(A2),COUNTIF(A:A,A2)=1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="14">
+      <formula>AND(MATCH(A2,A:A,0)=ROW(A2),COUNTIF(A:A,A2)&gt;1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="17" stopIfTrue="1">
+      <formula>MATCH(A2,A:A,0)&lt;&gt;ROW(A2)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
